--- a/docs/座標未取得_優先リスト.xlsx
+++ b/docs/座標未取得_優先リスト.xlsx
@@ -650,9 +650,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P3" s="5" t="n"/>
-      <c r="Q3" s="5" t="n"/>
-      <c r="R3" s="5" t="n"/>
+      <c r="P3" s="5" t="n">
+        <v>32.762095</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>130.700073</v>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 九州電力送配電近見変電所</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -716,9 +724,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="n"/>
-      <c r="R4" s="5" t="n"/>
+      <c r="P4" s="5" t="n">
+        <v>34.486482</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>133.357753</v>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 西町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -776,9 +792,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
+      <c r="P5" s="5" t="n">
+        <v>26.201722</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>127.689906</v>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）古波蔵変電所</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -840,9 +864,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
+      <c r="P6" s="5" t="n">
+        <v>26.324106</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>127.801947</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 島袋変電所</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -902,9 +934,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
+      <c r="P7" s="5" t="n">
+        <v>33.66408</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>130.414095</v>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 九州電力送配電アイランドシティ変電所</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1026,9 +1066,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
+      <c r="P9" s="5" t="n">
+        <v>33.309763</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>130.511987</v>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 原古賀変電所</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1088,9 +1136,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
+      <c r="P10" s="5" t="n">
+        <v>33.191945</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>131.611077</v>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 寒田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1150,9 +1206,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
+      <c r="P11" s="5" t="n">
+        <v>33.510719</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>130.470258</v>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 九州電力送配電平田台変電所</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1274,9 +1338,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
+      <c r="P13" s="5" t="n">
+        <v>33.383543</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>130.509555</v>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 神辺変電所</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1338,9 +1410,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
+      <c r="P14" s="5" t="n">
+        <v>37.646202</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>139.019128</v>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 保内変電所</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1402,9 +1482,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
+      <c r="P15" s="5" t="n">
+        <v>26.26872</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>127.720025</v>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 牧港第一変電所</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1712,9 +1800,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
+      <c r="P20" s="5" t="n">
+        <v>34.677145</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>135.503118</v>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 三休橋変電所</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1774,9 +1870,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
+      <c r="P21" s="5" t="n">
+        <v>34.691913</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>135.47986</v>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力亀甲町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1836,9 +1940,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
+      <c r="P22" s="5" t="n">
+        <v>34.685139</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>135.501221</v>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱備後町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -2022,9 +2134,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
+      <c r="P25" s="5" t="n">
+        <v>34.836608</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>135.51667</v>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱小野原変電所</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -2084,9 +2204,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
+      <c r="P26" s="5" t="n">
+        <v>35.267157</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>136.25928</v>
+      </c>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 彦根変電所</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -2208,9 +2336,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
+      <c r="P28" s="5" t="n">
+        <v>34.99659</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>135.765437</v>
+      </c>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 有隣変電所</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -2270,9 +2406,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
+      <c r="P29" s="5" t="n">
+        <v>34.687411</v>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>135.490524</v>
+      </c>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力江戸堀変電所</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -2336,9 +2480,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="5" t="n"/>
+      <c r="P30" s="5" t="n">
+        <v>34.578405</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>133.724352</v>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 西阿知変電所</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -2396,9 +2548,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="5" t="n"/>
-      <c r="R31" s="5" t="n"/>
+      <c r="P31" s="5" t="n">
+        <v>26.247588</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>127.690957</v>
+      </c>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 勢理客変電所</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -2456,9 +2616,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="5" t="n"/>
-      <c r="R32" s="5" t="n"/>
+      <c r="P32" s="5" t="n">
+        <v>26.211306</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>127.673887</v>
+      </c>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）東町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -2516,9 +2684,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
+      <c r="P33" s="5" t="n">
+        <v>26.212579</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>127.685268</v>
+      </c>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 松尾変電所</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -2644,9 +2820,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="n"/>
+      <c r="P35" s="5" t="n">
+        <v>26.214965</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>127.693582</v>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 牧志変電所</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -2704,9 +2888,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="5" t="n"/>
-      <c r="R36" s="5" t="n"/>
+      <c r="P36" s="5" t="n">
+        <v>26.215427</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>127.712168</v>
+      </c>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 繁多川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -2766,9 +2958,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P37" s="5" t="n"/>
-      <c r="Q37" s="5" t="n"/>
-      <c r="R37" s="5" t="n"/>
+      <c r="P37" s="5" t="n">
+        <v>34.80315</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>135.594257</v>
+      </c>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電目垣変電所</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -2826,9 +3026,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P38" s="5" t="n"/>
-      <c r="Q38" s="5" t="n"/>
-      <c r="R38" s="5" t="n"/>
+      <c r="P38" s="5" t="n">
+        <v>26.465867</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>127.935216</v>
+      </c>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）ギンバル変電所</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -2890,9 +3098,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P39" s="5" t="n"/>
-      <c r="Q39" s="5" t="n"/>
-      <c r="R39" s="5" t="n"/>
+      <c r="P39" s="5" t="n">
+        <v>26.674317</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>127.97868</v>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）今帰仁変電所</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -2954,9 +3170,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P40" s="5" t="n"/>
-      <c r="Q40" s="5" t="n"/>
-      <c r="R40" s="5" t="n"/>
+      <c r="P40" s="5" t="n">
+        <v>26.433266</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>127.81526</v>
+      </c>
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 仲石変電所</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -3014,9 +3238,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P41" s="5" t="n"/>
-      <c r="Q41" s="5" t="n"/>
-      <c r="R41" s="5" t="n"/>
+      <c r="P41" s="5" t="n">
+        <v>26.325534</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>127.756874</v>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力㈱伊平変電所</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -3074,9 +3306,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P42" s="5" t="n"/>
-      <c r="Q42" s="5" t="n"/>
-      <c r="R42" s="5" t="n"/>
+      <c r="P42" s="5" t="n">
+        <v>26.382612</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>127.757263</v>
+      </c>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 伊良皆第一変電所</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -3134,9 +3374,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P43" s="5" t="n"/>
-      <c r="Q43" s="5" t="n"/>
-      <c r="R43" s="5" t="n"/>
+      <c r="P43" s="5" t="n">
+        <v>26.127811</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>127.75135</v>
+      </c>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 具志頭変電所</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -3198,9 +3446,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P44" s="5" t="n"/>
-      <c r="Q44" s="5" t="n"/>
-      <c r="R44" s="5" t="n"/>
+      <c r="P44" s="5" t="n">
+        <v>26.456069</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>127.826047</v>
+      </c>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）冨着変電所</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -3258,9 +3514,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P45" s="5" t="n"/>
-      <c r="Q45" s="5" t="n"/>
-      <c r="R45" s="5" t="n"/>
+      <c r="P45" s="5" t="n">
+        <v>26.535615</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>127.93954</v>
+      </c>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）喜瀬変電所</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -3318,9 +3582,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P46" s="5" t="n"/>
-      <c r="Q46" s="5" t="n"/>
-      <c r="R46" s="5" t="n"/>
+      <c r="P46" s="5" t="n">
+        <v>26.393321</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>127.853124</v>
+      </c>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）天願変電所</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -3378,9 +3650,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P47" s="5" t="n"/>
-      <c r="Q47" s="5" t="n"/>
-      <c r="R47" s="5" t="n"/>
+      <c r="P47" s="5" t="n">
+        <v>26.222013</v>
+      </c>
+      <c r="Q47" s="5" t="n">
+        <v>127.757391</v>
+      </c>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 安室変電所</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -3438,9 +3718,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P48" s="5" t="n"/>
-      <c r="Q48" s="5" t="n"/>
-      <c r="R48" s="5" t="n"/>
+      <c r="P48" s="5" t="n">
+        <v>26.4977</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>127.883815</v>
+      </c>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）安富祖変電所</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -3502,9 +3790,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P49" s="5" t="n"/>
-      <c r="Q49" s="5" t="n"/>
-      <c r="R49" s="5" t="n"/>
+      <c r="P49" s="5" t="n">
+        <v>26.289277</v>
+      </c>
+      <c r="Q49" s="5" t="n">
+        <v>127.784548</v>
+      </c>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 安谷屋変電所</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -3562,9 +3858,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P50" s="5" t="n"/>
-      <c r="Q50" s="5" t="n"/>
-      <c r="R50" s="5" t="n"/>
+      <c r="P50" s="5" t="n">
+        <v>26.490746</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>127.84743</v>
+      </c>
+      <c r="R50" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）恩納変電所</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -3622,9 +3926,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P51" s="5" t="n"/>
-      <c r="Q51" s="5" t="n"/>
-      <c r="R51" s="5" t="n"/>
+      <c r="P51" s="5" t="n">
+        <v>26.277085</v>
+      </c>
+      <c r="Q51" s="5" t="n">
+        <v>127.748531</v>
+      </c>
+      <c r="R51" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）普天間変電所</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -3682,9 +3994,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P52" s="5" t="n"/>
-      <c r="Q52" s="5" t="n"/>
-      <c r="R52" s="5" t="n"/>
+      <c r="P52" s="5" t="n">
+        <v>26.310336</v>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>127.768797</v>
+      </c>
+      <c r="R52" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）桑江変電所</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -3742,9 +4062,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P53" s="5" t="n"/>
-      <c r="Q53" s="5" t="n"/>
-      <c r="R53" s="5" t="n"/>
+      <c r="P53" s="5" t="n">
+        <v>26.306987</v>
+      </c>
+      <c r="Q53" s="5" t="n">
+        <v>127.782076</v>
+      </c>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 瑞慶覧変電所</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -3802,9 +4130,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P54" s="5" t="n"/>
-      <c r="Q54" s="5" t="n"/>
-      <c r="R54" s="5" t="n"/>
+      <c r="P54" s="5" t="n">
+        <v>26.44183</v>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>127.834535</v>
+      </c>
+      <c r="R54" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 石川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -3862,9 +4198,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P55" s="5" t="n"/>
-      <c r="Q55" s="5" t="n"/>
-      <c r="R55" s="5" t="n"/>
+      <c r="P55" s="5" t="n">
+        <v>26.613229</v>
+      </c>
+      <c r="Q55" s="5" t="n">
+        <v>128.011578</v>
+      </c>
+      <c r="R55" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）羽地変電所</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -3926,9 +4270,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P56" s="5" t="n"/>
-      <c r="Q56" s="5" t="n"/>
-      <c r="R56" s="5" t="n"/>
+      <c r="P56" s="5" t="n">
+        <v>26.525261</v>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>128.034158</v>
+      </c>
+      <c r="R56" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）辺野古変電所</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -3990,9 +4342,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P57" s="5" t="n"/>
-      <c r="Q57" s="5" t="n"/>
-      <c r="R57" s="5" t="n"/>
+      <c r="P57" s="5" t="n">
+        <v>38.251445</v>
+      </c>
+      <c r="Q57" s="5" t="n">
+        <v>140.308879</v>
+      </c>
+      <c r="R57" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ あかねヶ丘変電所</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -4054,9 +4414,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P58" s="5" t="n"/>
-      <c r="Q58" s="5" t="n"/>
-      <c r="R58" s="5" t="n"/>
+      <c r="P58" s="5" t="n">
+        <v>38.263501</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>140.876525</v>
+      </c>
+      <c r="R58" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 仙台本町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -4118,9 +4486,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P59" s="5" t="n"/>
-      <c r="Q59" s="5" t="n"/>
-      <c r="R59" s="5" t="n"/>
+      <c r="P59" s="5" t="n">
+        <v>37.66709</v>
+      </c>
+      <c r="Q59" s="5" t="n">
+        <v>139.053427</v>
+      </c>
+      <c r="R59" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク（株） 加茂変電所</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -4182,9 +4558,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P60" s="5" t="n"/>
-      <c r="Q60" s="5" t="n"/>
-      <c r="R60" s="5" t="n"/>
+      <c r="P60" s="5" t="n">
+        <v>37.6403</v>
+      </c>
+      <c r="Q60" s="5" t="n">
+        <v>138.958912</v>
+      </c>
+      <c r="R60" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 北三条変電所</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -4246,9 +4630,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P61" s="5" t="n"/>
-      <c r="Q61" s="5" t="n"/>
-      <c r="R61" s="5" t="n"/>
+      <c r="P61" s="5" t="n">
+        <v>37.470196</v>
+      </c>
+      <c r="Q61" s="5" t="n">
+        <v>138.880139</v>
+      </c>
+      <c r="R61" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力北長岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -4310,9 +4702,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P62" s="5" t="n"/>
-      <c r="Q62" s="5" t="n"/>
-      <c r="R62" s="5" t="n"/>
+      <c r="P62" s="5" t="n">
+        <v>39.710999</v>
+      </c>
+      <c r="Q62" s="5" t="n">
+        <v>140.124722</v>
+      </c>
+      <c r="R62" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 南通変電所</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -4374,9 +4774,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P63" s="5" t="n"/>
-      <c r="Q63" s="5" t="n"/>
-      <c r="R63" s="5" t="n"/>
+      <c r="P63" s="5" t="n">
+        <v>37.074105</v>
+      </c>
+      <c r="Q63" s="5" t="n">
+        <v>138.259191</v>
+      </c>
+      <c r="R63" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 和田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -4438,9 +4846,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P64" s="5" t="n"/>
-      <c r="Q64" s="5" t="n"/>
-      <c r="R64" s="5" t="n"/>
+      <c r="P64" s="5" t="n">
+        <v>37.551407</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>139.830124</v>
+      </c>
+      <c r="R64" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 坂下変電所</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -4502,9 +4918,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P65" s="5" t="n"/>
-      <c r="Q65" s="5" t="n"/>
-      <c r="R65" s="5" t="n"/>
+      <c r="P65" s="5" t="n">
+        <v>37.095452</v>
+      </c>
+      <c r="Q65" s="5" t="n">
+        <v>138.904308</v>
+      </c>
+      <c r="R65" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 城内変電所</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -4566,9 +4990,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P66" s="5" t="n"/>
-      <c r="Q66" s="5" t="n"/>
-      <c r="R66" s="5" t="n"/>
+      <c r="P66" s="5" t="n">
+        <v>39.714925</v>
+      </c>
+      <c r="Q66" s="5" t="n">
+        <v>140.084267</v>
+      </c>
+      <c r="R66" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 大川反変電所</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -4630,9 +5062,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P67" s="5" t="n"/>
-      <c r="Q67" s="5" t="n"/>
-      <c r="R67" s="5" t="n"/>
+      <c r="P67" s="5" t="n">
+        <v>38.291313</v>
+      </c>
+      <c r="Q67" s="5" t="n">
+        <v>140.980405</v>
+      </c>
+      <c r="R67" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 大日変電所</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -4822,9 +5262,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P70" s="5" t="n"/>
-      <c r="Q70" s="5" t="n"/>
-      <c r="R70" s="5" t="n"/>
+      <c r="P70" s="5" t="n">
+        <v>38.285244</v>
+      </c>
+      <c r="Q70" s="5" t="n">
+        <v>140.936772</v>
+      </c>
+      <c r="R70" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 小鶴新田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -4886,9 +5334,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P71" s="5" t="n"/>
-      <c r="Q71" s="5" t="n"/>
-      <c r="R71" s="5" t="n"/>
+      <c r="P71" s="5" t="n">
+        <v>37.931911</v>
+      </c>
+      <c r="Q71" s="5" t="n">
+        <v>139.078166</v>
+      </c>
+      <c r="R71" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力山の下変電所</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -4950,9 +5406,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P72" s="5" t="n"/>
-      <c r="Q72" s="5" t="n"/>
-      <c r="R72" s="5" t="n"/>
+      <c r="P72" s="5" t="n">
+        <v>37.870535</v>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>139.079288</v>
+      </c>
+      <c r="R72" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 川根変電所</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -5014,9 +5478,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P73" s="5" t="n"/>
-      <c r="Q73" s="5" t="n"/>
-      <c r="R73" s="5" t="n"/>
+      <c r="P73" s="5" t="n">
+        <v>38.331867</v>
+      </c>
+      <c r="Q73" s="5" t="n">
+        <v>141.039581</v>
+      </c>
+      <c r="R73" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱新浜変電所</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -5142,9 +5614,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P75" s="5" t="n"/>
-      <c r="Q75" s="5" t="n"/>
-      <c r="R75" s="5" t="n"/>
+      <c r="P75" s="5" t="n">
+        <v>37.9192</v>
+      </c>
+      <c r="Q75" s="5" t="n">
+        <v>139.046886</v>
+      </c>
+      <c r="R75" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク（株）本町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -5270,9 +5750,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P77" s="5" t="n"/>
-      <c r="Q77" s="5" t="n"/>
-      <c r="R77" s="5" t="n"/>
+      <c r="P77" s="5" t="n">
+        <v>38.912405</v>
+      </c>
+      <c r="Q77" s="5" t="n">
+        <v>139.859857</v>
+      </c>
+      <c r="R77" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 東酒田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -5334,9 +5822,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P78" s="5" t="n"/>
-      <c r="Q78" s="5" t="n"/>
-      <c r="R78" s="5" t="n"/>
+      <c r="P78" s="5" t="n">
+        <v>38.366446</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>140.287895</v>
+      </c>
+      <c r="R78" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 栄町通変電所</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
@@ -5398,9 +5894,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P79" s="5" t="n"/>
-      <c r="Q79" s="5" t="n"/>
-      <c r="R79" s="5" t="n"/>
+      <c r="P79" s="5" t="n">
+        <v>37.917449</v>
+      </c>
+      <c r="Q79" s="5" t="n">
+        <v>139.062325</v>
+      </c>
+      <c r="R79" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 沼垂変電所</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -5462,9 +5966,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P80" s="5" t="n"/>
-      <c r="Q80" s="5" t="n"/>
-      <c r="R80" s="5" t="n"/>
+      <c r="P80" s="5" t="n">
+        <v>37.397035</v>
+      </c>
+      <c r="Q80" s="5" t="n">
+        <v>140.37606</v>
+      </c>
+      <c r="R80" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力細沼変電所</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
@@ -5590,9 +6102,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P82" s="5" t="n"/>
-      <c r="Q82" s="5" t="n"/>
-      <c r="R82" s="5" t="n"/>
+      <c r="P82" s="5" t="n">
+        <v>37.392349</v>
+      </c>
+      <c r="Q82" s="5" t="n">
+        <v>140.38665</v>
+      </c>
+      <c r="R82" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 郡山駅前変電所</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
@@ -5654,9 +6174,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P83" s="5" t="n"/>
-      <c r="Q83" s="5" t="n"/>
-      <c r="R83" s="5" t="n"/>
+      <c r="P83" s="5" t="n">
+        <v>39.731837</v>
+      </c>
+      <c r="Q83" s="5" t="n">
+        <v>141.118986</v>
+      </c>
+      <c r="R83" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 青山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
@@ -5718,9 +6246,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P84" s="5" t="n"/>
-      <c r="Q84" s="5" t="n"/>
-      <c r="R84" s="5" t="n"/>
+      <c r="P84" s="5" t="n">
+        <v>38.29656</v>
+      </c>
+      <c r="Q84" s="5" t="n">
+        <v>140.918218</v>
+      </c>
+      <c r="R84" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 鶴ヶ谷変電所</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
@@ -5780,9 +6316,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P85" s="5" t="n"/>
-      <c r="Q85" s="5" t="n"/>
-      <c r="R85" s="5" t="n"/>
+      <c r="P85" s="5" t="n">
+        <v>30.548577</v>
+      </c>
+      <c r="Q85" s="5" t="n">
+        <v>130.972271</v>
+      </c>
+      <c r="R85" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 九州電力送配電中種子変電所</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
@@ -5904,9 +6448,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P87" s="5" t="n"/>
-      <c r="Q87" s="5" t="n"/>
-      <c r="R87" s="5" t="n"/>
+      <c r="P87" s="5" t="n">
+        <v>33.210555</v>
+      </c>
+      <c r="Q87" s="5" t="n">
+        <v>130.399428</v>
+      </c>
+      <c r="R87" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 九州電力送配電木室変電所</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
@@ -6542,9 +7094,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P97" s="5" t="n"/>
-      <c r="Q97" s="5" t="n"/>
-      <c r="R97" s="5" t="n"/>
+      <c r="P97" s="5" t="n">
+        <v>39.823998</v>
+      </c>
+      <c r="Q97" s="5" t="n">
+        <v>140.640061</v>
+      </c>
+      <c r="R97" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 楢森変電所</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
@@ -6606,9 +7166,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P98" s="5" t="n"/>
-      <c r="Q98" s="5" t="n"/>
-      <c r="R98" s="5" t="n"/>
+      <c r="P98" s="5" t="n">
+        <v>36.916586</v>
+      </c>
+      <c r="Q98" s="5" t="n">
+        <v>138.806602</v>
+      </c>
+      <c r="R98" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株)神立変電所</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
@@ -6792,9 +7360,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P101" s="5" t="n"/>
-      <c r="Q101" s="5" t="n"/>
-      <c r="R101" s="5" t="n"/>
+      <c r="P101" s="5" t="n">
+        <v>34.729378</v>
+      </c>
+      <c r="Q101" s="5" t="n">
+        <v>135.493531</v>
+      </c>
+      <c r="R101" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力木川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
@@ -6854,9 +7430,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P102" s="5" t="n"/>
-      <c r="Q102" s="5" t="n"/>
-      <c r="R102" s="5" t="n"/>
+      <c r="P102" s="5" t="n">
+        <v>34.681021</v>
+      </c>
+      <c r="Q102" s="5" t="n">
+        <v>135.514846</v>
+      </c>
+      <c r="R102" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱農人橋変電所</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
@@ -6920,9 +7504,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P103" s="5" t="n"/>
-      <c r="Q103" s="5" t="n"/>
-      <c r="R103" s="5" t="n"/>
+      <c r="P103" s="5" t="n">
+        <v>34.536143</v>
+      </c>
+      <c r="Q103" s="5" t="n">
+        <v>133.279053</v>
+      </c>
+      <c r="R103" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 芦田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -6986,9 +7578,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P104" s="5" t="n"/>
-      <c r="Q104" s="5" t="n"/>
-      <c r="R104" s="5" t="n"/>
+      <c r="P104" s="5" t="n">
+        <v>34.603494</v>
+      </c>
+      <c r="Q104" s="5" t="n">
+        <v>133.741751</v>
+      </c>
+      <c r="R104" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 酒津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
@@ -7052,9 +7652,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P105" s="5" t="n"/>
-      <c r="Q105" s="5" t="n"/>
-      <c r="R105" s="5" t="n"/>
+      <c r="P105" s="5" t="n">
+        <v>34.57793</v>
+      </c>
+      <c r="Q105" s="5" t="n">
+        <v>133.757106</v>
+      </c>
+      <c r="R105" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 堀南変電所</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
@@ -7118,9 +7726,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P106" s="5" t="n"/>
-      <c r="Q106" s="5" t="n"/>
-      <c r="R106" s="5" t="n"/>
+      <c r="P106" s="5" t="n">
+        <v>34.611292</v>
+      </c>
+      <c r="Q106" s="5" t="n">
+        <v>133.765987</v>
+      </c>
+      <c r="R106" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 宮前変電所</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
@@ -7184,9 +7800,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P107" s="5" t="n"/>
-      <c r="Q107" s="5" t="n"/>
-      <c r="R107" s="5" t="n"/>
+      <c r="P107" s="5" t="n">
+        <v>34.423592</v>
+      </c>
+      <c r="Q107" s="5" t="n">
+        <v>133.213106</v>
+      </c>
+      <c r="R107" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東尾道変電所</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
@@ -7250,9 +7874,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P108" s="5" t="n"/>
-      <c r="Q108" s="5" t="n"/>
-      <c r="R108" s="5" t="n"/>
+      <c r="P108" s="5" t="n">
+        <v>34.491491</v>
+      </c>
+      <c r="Q108" s="5" t="n">
+        <v>133.369473</v>
+      </c>
+      <c r="R108" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
@@ -7316,9 +7948,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P109" s="5" t="n"/>
-      <c r="Q109" s="5" t="n"/>
-      <c r="R109" s="5" t="n"/>
+      <c r="P109" s="5" t="n">
+        <v>34.63107</v>
+      </c>
+      <c r="Q109" s="5" t="n">
+        <v>133.7917</v>
+      </c>
+      <c r="R109" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 生坂変電所</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
@@ -7382,9 +8022,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P110" s="5" t="n"/>
-      <c r="Q110" s="5" t="n"/>
-      <c r="R110" s="5" t="n"/>
+      <c r="P110" s="5" t="n">
+        <v>34.503422</v>
+      </c>
+      <c r="Q110" s="5" t="n">
+        <v>133.394517</v>
+      </c>
+      <c r="R110" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 蔵王変電所</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
@@ -7444,9 +8092,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P111" s="5" t="n"/>
-      <c r="Q111" s="5" t="n"/>
-      <c r="R111" s="5" t="n"/>
+      <c r="P111" s="5" t="n">
+        <v>35.023528</v>
+      </c>
+      <c r="Q111" s="5" t="n">
+        <v>135.775816</v>
+      </c>
+      <c r="R111" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 一条変電所</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
@@ -7506,9 +8162,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P112" s="5" t="n"/>
-      <c r="Q112" s="5" t="n"/>
-      <c r="R112" s="5" t="n"/>
+      <c r="P112" s="5" t="n">
+        <v>34.61102</v>
+      </c>
+      <c r="Q112" s="5" t="n">
+        <v>135.505531</v>
+      </c>
+      <c r="R112" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱上住吉変電所</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
@@ -7568,9 +8232,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P113" s="5" t="n"/>
-      <c r="Q113" s="5" t="n"/>
-      <c r="R113" s="5" t="n"/>
+      <c r="P113" s="5" t="n">
+        <v>34.796776</v>
+      </c>
+      <c r="Q113" s="5" t="n">
+        <v>135.496353</v>
+      </c>
+      <c r="R113" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱上新田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
@@ -7692,9 +8364,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P115" s="5" t="n"/>
-      <c r="Q115" s="5" t="n"/>
-      <c r="R115" s="5" t="n"/>
+      <c r="P115" s="5" t="n">
+        <v>34.950865</v>
+      </c>
+      <c r="Q115" s="5" t="n">
+        <v>135.691115</v>
+      </c>
+      <c r="R115" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱上里変電所</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
@@ -7754,9 +8434,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P116" s="5" t="n"/>
-      <c r="Q116" s="5" t="n"/>
-      <c r="R116" s="5" t="n"/>
+      <c r="P116" s="5" t="n">
+        <v>34.968429</v>
+      </c>
+      <c r="Q116" s="5" t="n">
+        <v>135.733632</v>
+      </c>
+      <c r="R116" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 上鳥羽変電所</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
@@ -7816,9 +8504,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P117" s="5" t="n"/>
-      <c r="Q117" s="5" t="n"/>
-      <c r="R117" s="5" t="n"/>
+      <c r="P117" s="5" t="n">
+        <v>35.47867</v>
+      </c>
+      <c r="Q117" s="5" t="n">
+        <v>135.367109</v>
+      </c>
+      <c r="R117" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 中舞鶴変電所</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
@@ -7878,9 +8574,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P118" s="5" t="n"/>
-      <c r="Q118" s="5" t="n"/>
-      <c r="R118" s="5" t="n"/>
+      <c r="P118" s="5" t="n">
+        <v>34.62135</v>
+      </c>
+      <c r="Q118" s="5" t="n">
+        <v>135.540304</v>
+      </c>
+      <c r="R118" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱中野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
@@ -8188,9 +8892,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P123" s="5" t="n"/>
-      <c r="Q123" s="5" t="n"/>
-      <c r="R123" s="5" t="n"/>
+      <c r="P123" s="5" t="n">
+        <v>34.834937</v>
+      </c>
+      <c r="Q123" s="5" t="n">
+        <v>135.603095</v>
+      </c>
+      <c r="R123" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 五百住変電所</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
@@ -8250,9 +8962,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P124" s="5" t="n"/>
-      <c r="Q124" s="5" t="n"/>
-      <c r="R124" s="5" t="n"/>
+      <c r="P124" s="5" t="n">
+        <v>34.669345</v>
+      </c>
+      <c r="Q124" s="5" t="n">
+        <v>135.823483</v>
+      </c>
+      <c r="R124" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電京終変電所</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
@@ -8312,9 +9032,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P125" s="5" t="n"/>
-      <c r="Q125" s="5" t="n"/>
-      <c r="R125" s="5" t="n"/>
+      <c r="P125" s="5" t="n">
+        <v>34.671705</v>
+      </c>
+      <c r="Q125" s="5" t="n">
+        <v>135.551484</v>
+      </c>
+      <c r="R125" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 今里変電所</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
@@ -8374,9 +9102,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P126" s="5" t="n"/>
-      <c r="Q126" s="5" t="n"/>
-      <c r="R126" s="5" t="n"/>
+      <c r="P126" s="5" t="n">
+        <v>34.92679</v>
+      </c>
+      <c r="Q126" s="5" t="n">
+        <v>135.757359</v>
+      </c>
+      <c r="R126" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 伏見変電所</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
@@ -8684,9 +9420,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P131" s="5" t="n"/>
-      <c r="Q131" s="5" t="n"/>
-      <c r="R131" s="5" t="n"/>
+      <c r="P131" s="5" t="n">
+        <v>34.753674</v>
+      </c>
+      <c r="Q131" s="5" t="n">
+        <v>135.504024</v>
+      </c>
+      <c r="R131" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電南金田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
@@ -8746,9 +9490,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P132" s="5" t="n"/>
-      <c r="Q132" s="5" t="n"/>
-      <c r="R132" s="5" t="n"/>
+      <c r="P132" s="5" t="n">
+        <v>34.976959</v>
+      </c>
+      <c r="Q132" s="5" t="n">
+        <v>135.739446</v>
+      </c>
+      <c r="R132" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 吉祥院変電所</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
@@ -8870,9 +9622,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P134" s="5" t="n"/>
-      <c r="Q134" s="5" t="n"/>
-      <c r="R134" s="5" t="n"/>
+      <c r="P134" s="5" t="n">
+        <v>35.024139</v>
+      </c>
+      <c r="Q134" s="5" t="n">
+        <v>135.752317</v>
+      </c>
+      <c r="R134" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力堀川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
@@ -8932,9 +9692,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P135" s="5" t="n"/>
-      <c r="Q135" s="5" t="n"/>
-      <c r="R135" s="5" t="n"/>
+      <c r="P135" s="5" t="n">
+        <v>34.70601</v>
+      </c>
+      <c r="Q135" s="5" t="n">
+        <v>135.484885</v>
+      </c>
+      <c r="R135" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力大仁変電所</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
@@ -8994,9 +9762,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P136" s="5" t="n"/>
-      <c r="Q136" s="5" t="n"/>
-      <c r="R136" s="5" t="n"/>
+      <c r="P136" s="5" t="n">
+        <v>34.98675</v>
+      </c>
+      <c r="Q136" s="5" t="n">
+        <v>135.772945</v>
+      </c>
+      <c r="R136" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 大仏変電所</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
@@ -9118,9 +9894,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P138" s="5" t="n"/>
-      <c r="Q138" s="5" t="n"/>
-      <c r="R138" s="5" t="n"/>
+      <c r="P138" s="5" t="n">
+        <v>34.983603</v>
+      </c>
+      <c r="Q138" s="5" t="n">
+        <v>135.832386</v>
+      </c>
+      <c r="R138" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 大塚変電所</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
@@ -9180,9 +9964,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P139" s="5" t="n"/>
-      <c r="Q139" s="5" t="n"/>
-      <c r="R139" s="5" t="n"/>
+      <c r="P139" s="5" t="n">
+        <v>34.903407</v>
+      </c>
+      <c r="Q139" s="5" t="n">
+        <v>135.685268</v>
+      </c>
+      <c r="R139" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 大山崎変電所</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
@@ -9304,9 +10096,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P141" s="5" t="n"/>
-      <c r="Q141" s="5" t="n"/>
-      <c r="R141" s="5" t="n"/>
+      <c r="P141" s="5" t="n">
+        <v>35.013616</v>
+      </c>
+      <c r="Q141" s="5" t="n">
+        <v>135.697359</v>
+      </c>
+      <c r="R141" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 太秦変電所</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
@@ -9428,9 +10228,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P143" s="5" t="n"/>
-      <c r="Q143" s="5" t="n"/>
-      <c r="R143" s="5" t="n"/>
+      <c r="P143" s="5" t="n">
+        <v>35.033945</v>
+      </c>
+      <c r="Q143" s="5" t="n">
+        <v>135.755152</v>
+      </c>
+      <c r="R143" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 室町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
@@ -9614,9 +10422,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P146" s="5" t="n"/>
-      <c r="Q146" s="5" t="n"/>
-      <c r="R146" s="5" t="n"/>
+      <c r="P146" s="5" t="n">
+        <v>34.773332</v>
+      </c>
+      <c r="Q146" s="5" t="n">
+        <v>135.516707</v>
+      </c>
+      <c r="R146" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 山手町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
@@ -9676,9 +10492,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P147" s="5" t="n"/>
-      <c r="Q147" s="5" t="n"/>
-      <c r="R147" s="5" t="n"/>
+      <c r="P147" s="5" t="n">
+        <v>35.048312</v>
+      </c>
+      <c r="Q147" s="5" t="n">
+        <v>135.788737</v>
+      </c>
+      <c r="R147" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 山端変電所</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
@@ -9738,9 +10562,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P148" s="5" t="n"/>
-      <c r="Q148" s="5" t="n"/>
-      <c r="R148" s="5" t="n"/>
+      <c r="P148" s="5" t="n">
+        <v>34.857677</v>
+      </c>
+      <c r="Q148" s="5" t="n">
+        <v>135.745454</v>
+      </c>
+      <c r="R148" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱ 岩田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
@@ -9800,9 +10632,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P149" s="5" t="n"/>
-      <c r="Q149" s="5" t="n"/>
-      <c r="R149" s="5" t="n"/>
+      <c r="P149" s="5" t="n">
+        <v>34.779555</v>
+      </c>
+      <c r="Q149" s="5" t="n">
+        <v>135.528064</v>
+      </c>
+      <c r="R149" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 岸部変電所</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
@@ -9986,9 +10826,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P152" s="5" t="n"/>
-      <c r="Q152" s="5" t="n"/>
-      <c r="R152" s="5" t="n"/>
+      <c r="P152" s="5" t="n">
+        <v>34.513003</v>
+      </c>
+      <c r="Q152" s="5" t="n">
+        <v>135.731585</v>
+      </c>
+      <c r="R152" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱市場変電所</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
@@ -10048,9 +10896,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P153" s="5" t="n"/>
-      <c r="Q153" s="5" t="n"/>
-      <c r="R153" s="5" t="n"/>
+      <c r="P153" s="5" t="n">
+        <v>35.216216</v>
+      </c>
+      <c r="Q153" s="5" t="n">
+        <v>135.135108</v>
+      </c>
+      <c r="R153" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 市島変電所</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
@@ -10110,9 +10966,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P154" s="5" t="n"/>
-      <c r="Q154" s="5" t="n"/>
-      <c r="R154" s="5" t="n"/>
+      <c r="P154" s="5" t="n">
+        <v>34.624202</v>
+      </c>
+      <c r="Q154" s="5" t="n">
+        <v>135.504313</v>
+      </c>
+      <c r="R154" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱帝塚山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
@@ -10172,9 +11036,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P155" s="5" t="n"/>
-      <c r="Q155" s="5" t="n"/>
-      <c r="R155" s="5" t="n"/>
+      <c r="P155" s="5" t="n">
+        <v>34.56094</v>
+      </c>
+      <c r="Q155" s="5" t="n">
+        <v>135.571497</v>
+      </c>
+      <c r="R155" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 恵我之荘変電所</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
@@ -10358,9 +11230,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P158" s="5" t="n"/>
-      <c r="Q158" s="5" t="n"/>
-      <c r="R158" s="5" t="n"/>
+      <c r="P158" s="5" t="n">
+        <v>35.005311</v>
+      </c>
+      <c r="Q158" s="5" t="n">
+        <v>135.733692</v>
+      </c>
+      <c r="R158" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 朱雀野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
@@ -10420,9 +11300,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P159" s="5" t="n"/>
-      <c r="Q159" s="5" t="n"/>
-      <c r="R159" s="5" t="n"/>
+      <c r="P159" s="5" t="n">
+        <v>34.582411</v>
+      </c>
+      <c r="Q159" s="5" t="n">
+        <v>135.488875</v>
+      </c>
+      <c r="R159" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱東堺変電所</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
@@ -10482,9 +11370,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P160" s="5" t="n"/>
-      <c r="Q160" s="5" t="n"/>
-      <c r="R160" s="5" t="n"/>
+      <c r="P160" s="5" t="n">
+        <v>34.981562</v>
+      </c>
+      <c r="Q160" s="5" t="n">
+        <v>135.756162</v>
+      </c>
+      <c r="R160" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 東寺変電所</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
@@ -10668,9 +11564,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P163" s="5" t="n"/>
-      <c r="Q163" s="5" t="n"/>
-      <c r="R163" s="5" t="n"/>
+      <c r="P163" s="5" t="n">
+        <v>34.488077</v>
+      </c>
+      <c r="Q163" s="5" t="n">
+        <v>135.798284</v>
+      </c>
+      <c r="R163" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電栄和町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
@@ -10730,9 +11634,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P164" s="5" t="n"/>
-      <c r="Q164" s="5" t="n"/>
-      <c r="R164" s="5" t="n"/>
+      <c r="P164" s="5" t="n">
+        <v>34.861087</v>
+      </c>
+      <c r="Q164" s="5" t="n">
+        <v>135.685657</v>
+      </c>
+      <c r="R164" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 楠葉変電所</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
@@ -10792,9 +11704,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P165" s="5" t="n"/>
-      <c r="Q165" s="5" t="n"/>
-      <c r="R165" s="5" t="n"/>
+      <c r="P165" s="5" t="n">
+        <v>34.776799</v>
+      </c>
+      <c r="Q165" s="5" t="n">
+        <v>135.549967</v>
+      </c>
+      <c r="R165" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 正雀変電所</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
@@ -10854,9 +11774,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P166" s="5" t="n"/>
-      <c r="Q166" s="5" t="n"/>
-      <c r="R166" s="5" t="n"/>
+      <c r="P166" s="5" t="n">
+        <v>34.885974</v>
+      </c>
+      <c r="Q166" s="5" t="n">
+        <v>135.660713</v>
+      </c>
+      <c r="R166" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 水無瀬変電所</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
@@ -10916,9 +11844,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P167" s="5" t="n"/>
-      <c r="Q167" s="5" t="n"/>
-      <c r="R167" s="5" t="n"/>
+      <c r="P167" s="5" t="n">
+        <v>34.671112</v>
+      </c>
+      <c r="Q167" s="5" t="n">
+        <v>135.468817</v>
+      </c>
+      <c r="R167" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力波除変電所</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
@@ -10978,9 +11914,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P168" s="5" t="n"/>
-      <c r="Q168" s="5" t="n"/>
-      <c r="R168" s="5" t="n"/>
+      <c r="P168" s="5" t="n">
+        <v>35.01089</v>
+      </c>
+      <c r="Q168" s="5" t="n">
+        <v>135.865195</v>
+      </c>
+      <c r="R168" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 浜大津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
@@ -11226,9 +12170,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P172" s="5" t="n"/>
-      <c r="Q172" s="5" t="n"/>
-      <c r="R172" s="5" t="n"/>
+      <c r="P172" s="5" t="n">
+        <v>34.603471</v>
+      </c>
+      <c r="Q172" s="5" t="n">
+        <v>135.552774</v>
+      </c>
+      <c r="R172" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力瓜破変電所</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
@@ -11288,9 +12240,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P173" s="5" t="n"/>
-      <c r="Q173" s="5" t="n"/>
-      <c r="R173" s="5" t="n"/>
+      <c r="P173" s="5" t="n">
+        <v>35.034874</v>
+      </c>
+      <c r="Q173" s="5" t="n">
+        <v>135.729814</v>
+      </c>
+      <c r="R173" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 白梅町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
@@ -11474,9 +12434,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P176" s="5" t="n"/>
-      <c r="Q176" s="5" t="n"/>
-      <c r="R176" s="5" t="n"/>
+      <c r="P176" s="5" t="n">
+        <v>34.868156</v>
+      </c>
+      <c r="Q176" s="5" t="n">
+        <v>135.610656</v>
+      </c>
+      <c r="R176" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電真上町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
@@ -11536,9 +12504,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P177" s="5" t="n"/>
-      <c r="Q177" s="5" t="n"/>
-      <c r="R177" s="5" t="n"/>
+      <c r="P177" s="5" t="n">
+        <v>34.634601</v>
+      </c>
+      <c r="Q177" s="5" t="n">
+        <v>135.611893</v>
+      </c>
+      <c r="R177" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 緑ヶ丘変電所</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
@@ -11598,9 +12574,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P178" s="5" t="n"/>
-      <c r="Q178" s="5" t="n"/>
-      <c r="R178" s="5" t="n"/>
+      <c r="P178" s="5" t="n">
+        <v>34.634664</v>
+      </c>
+      <c r="Q178" s="5" t="n">
+        <v>135.525208</v>
+      </c>
+      <c r="R178" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 美章園変電所</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
@@ -11784,9 +12768,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P181" s="5" t="n"/>
-      <c r="Q181" s="5" t="n"/>
-      <c r="R181" s="5" t="n"/>
+      <c r="P181" s="5" t="n">
+        <v>34.686332</v>
+      </c>
+      <c r="Q181" s="5" t="n">
+        <v>135.775693</v>
+      </c>
+      <c r="R181" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 菅原町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
@@ -11908,9 +12900,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P183" s="5" t="n"/>
-      <c r="Q183" s="5" t="n"/>
-      <c r="R183" s="5" t="n"/>
+      <c r="P183" s="5" t="n">
+        <v>34.503831</v>
+      </c>
+      <c r="Q183" s="5" t="n">
+        <v>135.477524</v>
+      </c>
+      <c r="R183" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 菱木変電所</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n">
@@ -11970,9 +12970,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P184" s="5" t="n"/>
-      <c r="Q184" s="5" t="n"/>
-      <c r="R184" s="5" t="n"/>
+      <c r="P184" s="5" t="n">
+        <v>34.833603</v>
+      </c>
+      <c r="Q184" s="5" t="n">
+        <v>135.623827</v>
+      </c>
+      <c r="R184" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電西天川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
@@ -12032,9 +13040,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P185" s="5" t="n"/>
-      <c r="Q185" s="5" t="n"/>
-      <c r="R185" s="5" t="n"/>
+      <c r="P185" s="5" t="n">
+        <v>34.976506</v>
+      </c>
+      <c r="Q185" s="5" t="n">
+        <v>135.797308</v>
+      </c>
+      <c r="R185" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 西山科変電所</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n">
@@ -12280,9 +13296,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P189" s="5" t="n"/>
-      <c r="Q189" s="5" t="n"/>
-      <c r="R189" s="5" t="n"/>
+      <c r="P189" s="5" t="n">
+        <v>34.719994</v>
+      </c>
+      <c r="Q189" s="5" t="n">
+        <v>135.529376</v>
+      </c>
+      <c r="R189" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 赤川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n">
@@ -12528,9 +13552,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P193" s="5" t="n"/>
-      <c r="Q193" s="5" t="n"/>
-      <c r="R193" s="5" t="n"/>
+      <c r="P193" s="5" t="n">
+        <v>34.508644</v>
+      </c>
+      <c r="Q193" s="5" t="n">
+        <v>135.814062</v>
+      </c>
+      <c r="R193" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 香久山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n">
@@ -12590,9 +13622,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P194" s="5" t="n"/>
-      <c r="Q194" s="5" t="n"/>
-      <c r="R194" s="5" t="n"/>
+      <c r="P194" s="5" t="n">
+        <v>35.03944</v>
+      </c>
+      <c r="Q194" s="5" t="n">
+        <v>135.958843</v>
+      </c>
+      <c r="R194" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 駒井沢変電所</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n">
@@ -12652,9 +13692,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P195" s="5" t="n"/>
-      <c r="Q195" s="5" t="n"/>
-      <c r="R195" s="5" t="n"/>
+      <c r="P195" s="5" t="n">
+        <v>34.575129</v>
+      </c>
+      <c r="Q195" s="5" t="n">
+        <v>135.582535</v>
+      </c>
+      <c r="R195" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 高鷲変電所</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n">
@@ -12714,9 +13762,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P196" s="5" t="n"/>
-      <c r="Q196" s="5" t="n"/>
-      <c r="R196" s="5" t="n"/>
+      <c r="P196" s="5" t="n">
+        <v>34.658196</v>
+      </c>
+      <c r="Q196" s="5" t="n">
+        <v>135.532489</v>
+      </c>
+      <c r="R196" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力鶴橋変電所</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n">
@@ -12778,9 +13834,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P197" s="5" t="n"/>
-      <c r="Q197" s="5" t="n"/>
-      <c r="R197" s="5" t="n"/>
+      <c r="P197" s="5" t="n">
+        <v>26.333323</v>
+      </c>
+      <c r="Q197" s="5" t="n">
+        <v>127.877704</v>
+      </c>
+      <c r="R197" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）与勝変電所</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n">
@@ -12902,9 +13966,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P199" s="5" t="n"/>
-      <c r="Q199" s="5" t="n"/>
-      <c r="R199" s="5" t="n"/>
+      <c r="P199" s="5" t="n">
+        <v>26.3299</v>
+      </c>
+      <c r="Q199" s="5" t="n">
+        <v>127.85305</v>
+      </c>
+      <c r="R199" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力株式会社 中城湾変電所</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n">
@@ -12962,9 +14034,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P200" s="5" t="n"/>
-      <c r="Q200" s="5" t="n"/>
-      <c r="R200" s="5" t="n"/>
+      <c r="P200" s="5" t="n">
+        <v>26.411852</v>
+      </c>
+      <c r="Q200" s="5" t="n">
+        <v>127.822999</v>
+      </c>
+      <c r="R200" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 伊波変電所</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n">
@@ -13026,9 +14106,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P201" s="5" t="n"/>
-      <c r="Q201" s="5" t="n"/>
-      <c r="R201" s="5" t="n"/>
+      <c r="P201" s="5" t="n">
+        <v>26.30358</v>
+      </c>
+      <c r="Q201" s="5" t="n">
+        <v>127.759993</v>
+      </c>
+      <c r="R201" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北谷変電所</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n">
@@ -13090,9 +14178,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P202" s="5" t="n"/>
-      <c r="Q202" s="5" t="n"/>
-      <c r="R202" s="5" t="n"/>
+      <c r="P202" s="5" t="n">
+        <v>26.253349</v>
+      </c>
+      <c r="Q202" s="5" t="n">
+        <v>127.775884</v>
+      </c>
+      <c r="R202" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）南上原変電所</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n">
@@ -13154,9 +14250,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P203" s="5" t="n"/>
-      <c r="Q203" s="5" t="n"/>
-      <c r="R203" s="5" t="n"/>
+      <c r="P203" s="5" t="n">
+        <v>26.166341</v>
+      </c>
+      <c r="Q203" s="5" t="n">
+        <v>127.71933</v>
+      </c>
+      <c r="R203" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 友寄変電所</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n">
@@ -13214,9 +14318,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P204" s="5" t="n"/>
-      <c r="Q204" s="5" t="n"/>
-      <c r="R204" s="5" t="n"/>
+      <c r="P204" s="5" t="n">
+        <v>26.357883</v>
+      </c>
+      <c r="Q204" s="5" t="n">
+        <v>127.849179</v>
+      </c>
+      <c r="R204" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 喜仲変電所</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n">
@@ -13334,9 +14446,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P206" s="5" t="n"/>
-      <c r="Q206" s="5" t="n"/>
-      <c r="R206" s="5" t="n"/>
+      <c r="P206" s="5" t="n">
+        <v>26.232303</v>
+      </c>
+      <c r="Q206" s="5" t="n">
+        <v>127.723657</v>
+      </c>
+      <c r="R206" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力大名変電所</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n">
@@ -13398,9 +14518,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P207" s="5" t="n"/>
-      <c r="Q207" s="5" t="n"/>
-      <c r="R207" s="5" t="n"/>
+      <c r="P207" s="5" t="n">
+        <v>26.275912</v>
+      </c>
+      <c r="Q207" s="5" t="n">
+        <v>127.736475</v>
+      </c>
+      <c r="R207" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 大山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n">
@@ -13458,9 +14586,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P208" s="5" t="n"/>
-      <c r="Q208" s="5" t="n"/>
-      <c r="R208" s="5" t="n"/>
+      <c r="P208" s="5" t="n">
+        <v>26.611527</v>
+      </c>
+      <c r="Q208" s="5" t="n">
+        <v>127.936783</v>
+      </c>
+      <c r="R208" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）安和変電所</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n">
@@ -13518,9 +14654,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P209" s="5" t="n"/>
-      <c r="Q209" s="5" t="n"/>
-      <c r="R209" s="5" t="n"/>
+      <c r="P209" s="5" t="n">
+        <v>26.245356</v>
+      </c>
+      <c r="Q209" s="5" t="n">
+        <v>127.703083</v>
+      </c>
+      <c r="R209" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）宮城変電所</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n">
@@ -13578,9 +14722,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P210" s="5" t="n"/>
-      <c r="Q210" s="5" t="n"/>
-      <c r="R210" s="5" t="n"/>
+      <c r="P210" s="5" t="n">
+        <v>26.367009</v>
+      </c>
+      <c r="Q210" s="5" t="n">
+        <v>127.764753</v>
+      </c>
+      <c r="R210" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 屋良変電所</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n">
@@ -13638,9 +14790,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P211" s="5" t="n"/>
-      <c r="Q211" s="5" t="n"/>
-      <c r="R211" s="5" t="n"/>
+      <c r="P211" s="5" t="n">
+        <v>26.344769</v>
+      </c>
+      <c r="Q211" s="5" t="n">
+        <v>127.950041</v>
+      </c>
+      <c r="R211" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）平安座変電所</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n">
@@ -13698,9 +14858,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P212" s="5" t="n"/>
-      <c r="Q212" s="5" t="n"/>
-      <c r="R212" s="5" t="n"/>
+      <c r="P212" s="5" t="n">
+        <v>26.409138</v>
+      </c>
+      <c r="Q212" s="5" t="n">
+        <v>127.737868</v>
+      </c>
+      <c r="R212" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 座喜味変電所</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n">
@@ -13762,9 +14930,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P213" s="5" t="n"/>
-      <c r="Q213" s="5" t="n"/>
-      <c r="R213" s="5" t="n"/>
+      <c r="P213" s="5" t="n">
+        <v>26.610264</v>
+      </c>
+      <c r="Q213" s="5" t="n">
+        <v>127.986938</v>
+      </c>
+      <c r="R213" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）新名護変電所</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n">
@@ -13822,9 +14998,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P214" s="5" t="n"/>
-      <c r="Q214" s="5" t="n"/>
-      <c r="R214" s="5" t="n"/>
+      <c r="P214" s="5" t="n">
+        <v>26.456103</v>
+      </c>
+      <c r="Q214" s="5" t="n">
+        <v>127.921209</v>
+      </c>
+      <c r="R214" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）新金武変電所</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="n">
@@ -13886,9 +15070,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P215" s="5" t="n"/>
-      <c r="Q215" s="5" t="n"/>
-      <c r="R215" s="5" t="n"/>
+      <c r="P215" s="5" t="n">
+        <v>26.108649</v>
+      </c>
+      <c r="Q215" s="5" t="n">
+        <v>127.694237</v>
+      </c>
+      <c r="R215" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 真壁変電所</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n">
@@ -13946,9 +15138,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P216" s="5" t="n"/>
-      <c r="Q216" s="5" t="n"/>
-      <c r="R216" s="5" t="n"/>
+      <c r="P216" s="5" t="n">
+        <v>26.19394</v>
+      </c>
+      <c r="Q216" s="5" t="n">
+        <v>127.700795</v>
+      </c>
+      <c r="R216" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）真玉橋変電所</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="n">
@@ -14006,9 +15206,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P217" s="5" t="n"/>
-      <c r="Q217" s="5" t="n"/>
-      <c r="R217" s="5" t="n"/>
+      <c r="P217" s="5" t="n">
+        <v>26.35428</v>
+      </c>
+      <c r="Q217" s="5" t="n">
+        <v>127.806944</v>
+      </c>
+      <c r="R217" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 知花変電所</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n">
@@ -14066,9 +15274,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P218" s="5" t="n"/>
-      <c r="Q218" s="5" t="n"/>
-      <c r="R218" s="5" t="n"/>
+      <c r="P218" s="5" t="n">
+        <v>26.135676</v>
+      </c>
+      <c r="Q218" s="5" t="n">
+        <v>127.692136</v>
+      </c>
+      <c r="R218" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 糸満変電所</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n">
@@ -14130,9 +15346,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P219" s="5" t="n"/>
-      <c r="Q219" s="5" t="n"/>
-      <c r="R219" s="5" t="n"/>
+      <c r="P219" s="5" t="n">
+        <v>26.345551</v>
+      </c>
+      <c r="Q219" s="5" t="n">
+        <v>127.826302</v>
+      </c>
+      <c r="R219" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力 美里変電所</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n">
@@ -14190,9 +15414,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P220" s="5" t="n"/>
-      <c r="Q220" s="5" t="n"/>
-      <c r="R220" s="5" t="n"/>
+      <c r="P220" s="5" t="n">
+        <v>26.327649</v>
+      </c>
+      <c r="Q220" s="5" t="n">
+        <v>127.821092</v>
+      </c>
+      <c r="R220" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力 高原変電所</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n">
@@ -14250,9 +15482,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P221" s="5" t="n"/>
-      <c r="Q221" s="5" t="n"/>
-      <c r="R221" s="5" t="n"/>
+      <c r="P221" s="5" t="n">
+        <v>26.175436</v>
+      </c>
+      <c r="Q221" s="5" t="n">
+        <v>127.687709</v>
+      </c>
+      <c r="R221" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力 高安変電所</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n">
@@ -14436,9 +15676,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P224" s="5" t="n"/>
-      <c r="Q224" s="5" t="n"/>
-      <c r="R224" s="5" t="n"/>
+      <c r="P224" s="5" t="n">
+        <v>35.735132</v>
+      </c>
+      <c r="Q224" s="5" t="n">
+        <v>139.677001</v>
+      </c>
+      <c r="R224" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 江古田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n">
@@ -14498,9 +15746,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P225" s="5" t="n"/>
-      <c r="Q225" s="5" t="n"/>
-      <c r="R225" s="5" t="n"/>
+      <c r="P225" s="5" t="n">
+        <v>35.708764</v>
+      </c>
+      <c r="Q225" s="5" t="n">
+        <v>139.411713</v>
+      </c>
+      <c r="R225" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東京電力パワーグリッド（株）緑町変電所（地下変電所）</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n">
@@ -14560,9 +15816,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P226" s="5" t="n"/>
-      <c r="Q226" s="5" t="n"/>
-      <c r="R226" s="5" t="n"/>
+      <c r="P226" s="5" t="n">
+        <v>35.723011</v>
+      </c>
+      <c r="Q226" s="5" t="n">
+        <v>139.683232</v>
+      </c>
+      <c r="R226" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東京電力パワーグリッド㈱ 西落合変電所</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="3" t="n">
@@ -14624,9 +15888,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P227" s="5" t="n"/>
-      <c r="Q227" s="5" t="n"/>
-      <c r="R227" s="5" t="n"/>
+      <c r="P227" s="5" t="n">
+        <v>37.411783</v>
+      </c>
+      <c r="Q227" s="5" t="n">
+        <v>140.378734</v>
+      </c>
+      <c r="R227" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 久保田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n">
@@ -14688,9 +15960,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P228" s="5" t="n"/>
-      <c r="Q228" s="5" t="n"/>
-      <c r="R228" s="5" t="n"/>
+      <c r="P228" s="5" t="n">
+        <v>38.369987</v>
+      </c>
+      <c r="Q228" s="5" t="n">
+        <v>140.360909</v>
+      </c>
+      <c r="R228" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 久野本変電所</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="n">
@@ -14752,9 +16032,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P229" s="5" t="n"/>
-      <c r="Q229" s="5" t="n"/>
-      <c r="R229" s="5" t="n"/>
+      <c r="P229" s="5" t="n">
+        <v>37.866815</v>
+      </c>
+      <c r="Q229" s="5" t="n">
+        <v>139.102441</v>
+      </c>
+      <c r="R229" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力亀田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n">
@@ -14816,9 +16104,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P230" s="5" t="n"/>
-      <c r="Q230" s="5" t="n"/>
-      <c r="R230" s="5" t="n"/>
+      <c r="P230" s="5" t="n">
+        <v>37.866303</v>
+      </c>
+      <c r="Q230" s="5" t="n">
+        <v>138.982032</v>
+      </c>
+      <c r="R230" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 亀貝変電所</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="3" t="n">
@@ -14880,9 +16176,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P231" s="5" t="n"/>
-      <c r="Q231" s="5" t="n"/>
-      <c r="R231" s="5" t="n"/>
+      <c r="P231" s="5" t="n">
+        <v>39.682721</v>
+      </c>
+      <c r="Q231" s="5" t="n">
+        <v>141.13064</v>
+      </c>
+      <c r="R231" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 仙北町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="n">
@@ -15008,9 +16312,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P233" s="5" t="n"/>
-      <c r="Q233" s="5" t="n"/>
-      <c r="R233" s="5" t="n"/>
+      <c r="P233" s="5" t="n">
+        <v>38.25249</v>
+      </c>
+      <c r="Q233" s="5" t="n">
+        <v>140.920421</v>
+      </c>
+      <c r="R233" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 卸町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n">
@@ -15136,9 +16448,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P235" s="5" t="n"/>
-      <c r="Q235" s="5" t="n"/>
-      <c r="R235" s="5" t="n"/>
+      <c r="P235" s="5" t="n">
+        <v>37.486531</v>
+      </c>
+      <c r="Q235" s="5" t="n">
+        <v>139.937238</v>
+      </c>
+      <c r="R235" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 城東変電所</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n">
@@ -15200,9 +16520,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P236" s="5" t="n"/>
-      <c r="Q236" s="5" t="n"/>
-      <c r="R236" s="5" t="n"/>
+      <c r="P236" s="5" t="n">
+        <v>37.45028</v>
+      </c>
+      <c r="Q236" s="5" t="n">
+        <v>138.8526</v>
+      </c>
+      <c r="R236" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株)大手変電所</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n">
@@ -15264,9 +16592,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P237" s="5" t="n"/>
-      <c r="Q237" s="5" t="n"/>
-      <c r="R237" s="5" t="n"/>
+      <c r="P237" s="5" t="n">
+        <v>37.22753</v>
+      </c>
+      <c r="Q237" s="5" t="n">
+        <v>140.583232</v>
+      </c>
+      <c r="R237" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 平田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n">
@@ -15456,9 +16792,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P240" s="5" t="n"/>
-      <c r="Q240" s="5" t="n"/>
-      <c r="R240" s="5" t="n"/>
+      <c r="P240" s="5" t="n">
+        <v>38.237795</v>
+      </c>
+      <c r="Q240" s="5" t="n">
+        <v>140.355662</v>
+      </c>
+      <c r="R240" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株)松波変電所</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="3" t="n">
@@ -15712,9 +17056,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P244" s="5" t="n"/>
-      <c r="Q244" s="5" t="n"/>
-      <c r="R244" s="5" t="n"/>
+      <c r="P244" s="5" t="n">
+        <v>37.910653</v>
+      </c>
+      <c r="Q244" s="5" t="n">
+        <v>139.033986</v>
+      </c>
+      <c r="R244" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 白山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="3" t="n">
@@ -15776,9 +17128,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P245" s="5" t="n"/>
-      <c r="Q245" s="5" t="n"/>
-      <c r="R245" s="5" t="n"/>
+      <c r="P245" s="5" t="n">
+        <v>39.701664</v>
+      </c>
+      <c r="Q245" s="5" t="n">
+        <v>141.157224</v>
+      </c>
+      <c r="R245" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 盛岡中央変電所</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="n">
@@ -15840,9 +17200,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P246" s="5" t="n"/>
-      <c r="Q246" s="5" t="n"/>
-      <c r="R246" s="5" t="n"/>
+      <c r="P246" s="5" t="n">
+        <v>38.260784</v>
+      </c>
+      <c r="Q246" s="5" t="n">
+        <v>140.948988</v>
+      </c>
+      <c r="R246" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 福田町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="3" t="n">
@@ -15904,9 +17272,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P247" s="5" t="n"/>
-      <c r="Q247" s="5" t="n"/>
-      <c r="R247" s="5" t="n"/>
+      <c r="P247" s="5" t="n">
+        <v>37.933543</v>
+      </c>
+      <c r="Q247" s="5" t="n">
+        <v>139.098961</v>
+      </c>
+      <c r="R247" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 藤見変電所</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="3" t="n">
@@ -15968,9 +17344,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P248" s="5" t="n"/>
-      <c r="Q248" s="5" t="n"/>
-      <c r="R248" s="5" t="n"/>
+      <c r="P248" s="5" t="n">
+        <v>39.728967</v>
+      </c>
+      <c r="Q248" s="5" t="n">
+        <v>141.133262</v>
+      </c>
+      <c r="R248" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 高松変電所</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="3" t="n">
@@ -16030,9 +17414,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P249" s="5" t="n"/>
-      <c r="Q249" s="5" t="n"/>
-      <c r="R249" s="5" t="n"/>
+      <c r="P249" s="5" t="n">
+        <v>33.516662</v>
+      </c>
+      <c r="Q249" s="5" t="n">
+        <v>130.439663</v>
+      </c>
+      <c r="R249" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 九州電力送配電上白水変電所</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="3" t="n">
@@ -16092,9 +17484,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P250" s="5" t="n"/>
-      <c r="Q250" s="5" t="n"/>
-      <c r="R250" s="5" t="n"/>
+      <c r="P250" s="5" t="n">
+        <v>33.223234</v>
+      </c>
+      <c r="Q250" s="5" t="n">
+        <v>130.556926</v>
+      </c>
+      <c r="R250" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 九州電力送配電八女変電所</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="3" t="n">
@@ -16216,9 +17616,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P252" s="5" t="n"/>
-      <c r="Q252" s="5" t="n"/>
-      <c r="R252" s="5" t="n"/>
+      <c r="P252" s="5" t="n">
+        <v>33.567407</v>
+      </c>
+      <c r="Q252" s="5" t="n">
+        <v>130.242187</v>
+      </c>
+      <c r="R252" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 周船寺変電所</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="3" t="n">
@@ -16278,9 +17686,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P253" s="5" t="n"/>
-      <c r="Q253" s="5" t="n"/>
-      <c r="R253" s="5" t="n"/>
+      <c r="P253" s="5" t="n">
+        <v>33.564338</v>
+      </c>
+      <c r="Q253" s="5" t="n">
+        <v>130.507126</v>
+      </c>
+      <c r="R253" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 九州電力送配電宇美変電所</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="3" t="n">
@@ -16340,9 +17756,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P254" s="5" t="n"/>
-      <c r="Q254" s="5" t="n"/>
-      <c r="R254" s="5" t="n"/>
+      <c r="P254" s="5" t="n">
+        <v>33.259924</v>
+      </c>
+      <c r="Q254" s="5" t="n">
+        <v>130.546682</v>
+      </c>
+      <c r="R254" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 九州電力送配電広川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="3" t="n">
@@ -16464,9 +17888,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P256" s="5" t="n"/>
-      <c r="Q256" s="5" t="n"/>
-      <c r="R256" s="5" t="n"/>
+      <c r="P256" s="5" t="n">
+        <v>33.315632</v>
+      </c>
+      <c r="Q256" s="5" t="n">
+        <v>130.517826</v>
+      </c>
+      <c r="R256" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="3" t="n">
@@ -16526,9 +17958,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P257" s="5" t="n"/>
-      <c r="Q257" s="5" t="n"/>
-      <c r="R257" s="5" t="n"/>
+      <c r="P257" s="5" t="n">
+        <v>33.169743</v>
+      </c>
+      <c r="Q257" s="5" t="n">
+        <v>130.410886</v>
+      </c>
+      <c r="R257" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 九州電力送配電柳川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="n">
@@ -16650,9 +18090,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P259" s="5" t="n"/>
-      <c r="Q259" s="5" t="n"/>
-      <c r="R259" s="5" t="n"/>
+      <c r="P259" s="5" t="n">
+        <v>35.149047</v>
+      </c>
+      <c r="Q259" s="5" t="n">
+        <v>138.904695</v>
+      </c>
+      <c r="R259" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東京電力パワーグリッド(株) 堰原変電所</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="n">
@@ -16712,9 +18160,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P260" s="5" t="n"/>
-      <c r="Q260" s="5" t="n"/>
-      <c r="R260" s="5" t="n"/>
+      <c r="P260" s="5" t="n">
+        <v>35.439494</v>
+      </c>
+      <c r="Q260" s="5" t="n">
+        <v>138.918244</v>
+      </c>
+      <c r="R260" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東京電力パワーグリッド株式会社 平野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="n">
@@ -16836,9 +18292,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P262" s="5" t="n"/>
-      <c r="Q262" s="5" t="n"/>
-      <c r="R262" s="5" t="n"/>
+      <c r="P262" s="5" t="n">
+        <v>35.488181</v>
+      </c>
+      <c r="Q262" s="5" t="n">
+        <v>138.327752</v>
+      </c>
+      <c r="R262" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東京電力パワーグリッド 早川第三変電所</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="3" t="n">
@@ -16898,9 +18362,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P263" s="5" t="n"/>
-      <c r="Q263" s="5" t="n"/>
-      <c r="R263" s="5" t="n"/>
+      <c r="P263" s="5" t="n">
+        <v>35.166984</v>
+      </c>
+      <c r="Q263" s="5" t="n">
+        <v>138.63929</v>
+      </c>
+      <c r="R263" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東京電力パワーグリッド(株) 松岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="n">
@@ -17022,9 +18494,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P265" s="5" t="n"/>
-      <c r="Q265" s="5" t="n"/>
-      <c r="R265" s="5" t="n"/>
+      <c r="P265" s="5" t="n">
+        <v>35.598023</v>
+      </c>
+      <c r="Q265" s="5" t="n">
+        <v>138.931888</v>
+      </c>
+      <c r="R265" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 田野倉変電所</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="n">
@@ -17084,9 +18564,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P266" s="5" t="n"/>
-      <c r="Q266" s="5" t="n"/>
-      <c r="R266" s="5" t="n"/>
+      <c r="P266" s="5" t="n">
+        <v>35.324302</v>
+      </c>
+      <c r="Q266" s="5" t="n">
+        <v>139.112488</v>
+      </c>
+      <c r="R266" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 竹松変電所</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="3" t="n">
@@ -17208,9 +18696,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P268" s="5" t="n"/>
-      <c r="Q268" s="5" t="n"/>
-      <c r="R268" s="5" t="n"/>
+      <c r="P268" s="5" t="n">
+        <v>35.675411</v>
+      </c>
+      <c r="Q268" s="5" t="n">
+        <v>139.43651</v>
+      </c>
+      <c r="R268" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東京電力パワーグリッド(株) 谷保変電所</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="3" t="n">
@@ -17718,9 +19214,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P276" s="5" t="n"/>
-      <c r="Q276" s="5" t="n"/>
-      <c r="R276" s="5" t="n"/>
+      <c r="P276" s="5" t="n">
+        <v>38.851015</v>
+      </c>
+      <c r="Q276" s="5" t="n">
+        <v>139.889835</v>
+      </c>
+      <c r="R276" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 余目変電所</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="n">
@@ -17782,9 +19286,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P277" s="5" t="n"/>
-      <c r="Q277" s="5" t="n"/>
-      <c r="R277" s="5" t="n"/>
+      <c r="P277" s="5" t="n">
+        <v>37.685063</v>
+      </c>
+      <c r="Q277" s="5" t="n">
+        <v>139.034684</v>
+      </c>
+      <c r="R277" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 加茂郷変電所</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="n">
@@ -17846,9 +19358,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P278" s="5" t="n"/>
-      <c r="Q278" s="5" t="n"/>
-      <c r="R278" s="5" t="n"/>
+      <c r="P278" s="5" t="n">
+        <v>37.183633</v>
+      </c>
+      <c r="Q278" s="5" t="n">
+        <v>138.28679</v>
+      </c>
+      <c r="R278" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 南川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="3" t="n">
@@ -17910,9 +19430,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P279" s="5" t="n"/>
-      <c r="Q279" s="5" t="n"/>
-      <c r="R279" s="5" t="n"/>
+      <c r="P279" s="5" t="n">
+        <v>37.454636</v>
+      </c>
+      <c r="Q279" s="5" t="n">
+        <v>141.019339</v>
+      </c>
+      <c r="R279" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク双葉変電所</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="3" t="n">
@@ -17974,9 +19502,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P280" s="5" t="n"/>
-      <c r="Q280" s="5" t="n"/>
-      <c r="R280" s="5" t="n"/>
+      <c r="P280" s="5" t="n">
+        <v>39.674978</v>
+      </c>
+      <c r="Q280" s="5" t="n">
+        <v>141.147752</v>
+      </c>
+      <c r="R280" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 向中野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="n">
@@ -18038,9 +19574,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P281" s="5" t="n"/>
-      <c r="Q281" s="5" t="n"/>
-      <c r="R281" s="5" t="n"/>
+      <c r="P281" s="5" t="n">
+        <v>37.256364</v>
+      </c>
+      <c r="Q281" s="5" t="n">
+        <v>138.908238</v>
+      </c>
+      <c r="R281" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 堀之内変電所</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="n">
@@ -18102,9 +19646,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P282" s="5" t="n"/>
-      <c r="Q282" s="5" t="n"/>
-      <c r="R282" s="5" t="n"/>
+      <c r="P282" s="5" t="n">
+        <v>38.312479</v>
+      </c>
+      <c r="Q282" s="5" t="n">
+        <v>141.030878</v>
+      </c>
+      <c r="R282" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 塩釜築港変電所</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="3" t="n">
@@ -18230,9 +19782,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P284" s="5" t="n"/>
-      <c r="Q284" s="5" t="n"/>
-      <c r="R284" s="5" t="n"/>
+      <c r="P284" s="5" t="n">
+        <v>38.740046</v>
+      </c>
+      <c r="Q284" s="5" t="n">
+        <v>139.772367</v>
+      </c>
+      <c r="R284" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 大山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="3" t="n">
@@ -18294,9 +19854,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P285" s="5" t="n"/>
-      <c r="Q285" s="5" t="n"/>
-      <c r="R285" s="5" t="n"/>
+      <c r="P285" s="5" t="n">
+        <v>38.590559</v>
+      </c>
+      <c r="Q285" s="5" t="n">
+        <v>140.781777</v>
+      </c>
+      <c r="R285" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 宮崎変電所</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="n">
@@ -18358,9 +19926,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P286" s="5" t="n"/>
-      <c r="Q286" s="5" t="n"/>
-      <c r="R286" s="5" t="n"/>
+      <c r="P286" s="5" t="n">
+        <v>38.06459</v>
+      </c>
+      <c r="Q286" s="5" t="n">
+        <v>139.738981</v>
+      </c>
+      <c r="R286" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 小国変電所</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="n">
@@ -18422,9 +19998,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P287" s="5" t="n"/>
-      <c r="Q287" s="5" t="n"/>
-      <c r="R287" s="5" t="n"/>
+      <c r="P287" s="5" t="n">
+        <v>37.3066</v>
+      </c>
+      <c r="Q287" s="5" t="n">
+        <v>138.712687</v>
+      </c>
+      <c r="R287" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 小国町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="n">
@@ -18486,9 +20070,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P288" s="5" t="n"/>
-      <c r="Q288" s="5" t="n"/>
-      <c r="R288" s="5" t="n"/>
+      <c r="P288" s="5" t="n">
+        <v>37.747453</v>
+      </c>
+      <c r="Q288" s="5" t="n">
+        <v>138.839241</v>
+      </c>
+      <c r="R288" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 岩室変電所</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="3" t="n">
@@ -18550,9 +20142,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P289" s="5" t="n"/>
-      <c r="Q289" s="5" t="n"/>
-      <c r="R289" s="5" t="n"/>
+      <c r="P289" s="5" t="n">
+        <v>39.452256</v>
+      </c>
+      <c r="Q289" s="5" t="n">
+        <v>140.15537</v>
+      </c>
+      <c r="R289" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 岩谷変電所</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="n">
@@ -18614,9 +20214,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P290" s="5" t="n"/>
-      <c r="Q290" s="5" t="n"/>
-      <c r="R290" s="5" t="n"/>
+      <c r="P290" s="5" t="n">
+        <v>38.746187</v>
+      </c>
+      <c r="Q290" s="5" t="n">
+        <v>140.180923</v>
+      </c>
+      <c r="R290" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 戸沢変電所</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="3" t="n">
@@ -18678,9 +20286,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P291" s="5" t="n"/>
-      <c r="Q291" s="5" t="n"/>
-      <c r="R291" s="5" t="n"/>
+      <c r="P291" s="5" t="n">
+        <v>39.680475</v>
+      </c>
+      <c r="Q291" s="5" t="n">
+        <v>140.088658</v>
+      </c>
+      <c r="R291" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 新屋変電所</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="n">
@@ -18742,9 +20358,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P292" s="5" t="n"/>
-      <c r="Q292" s="5" t="n"/>
-      <c r="R292" s="5" t="n"/>
+      <c r="P292" s="5" t="n">
+        <v>38.790431</v>
+      </c>
+      <c r="Q292" s="5" t="n">
+        <v>140.303919</v>
+      </c>
+      <c r="R292" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 新庄十日町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="3" t="n">
@@ -18806,9 +20430,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P293" s="5" t="n"/>
-      <c r="Q293" s="5" t="n"/>
-      <c r="R293" s="5" t="n"/>
+      <c r="P293" s="5" t="n">
+        <v>37.474225</v>
+      </c>
+      <c r="Q293" s="5" t="n">
+        <v>140.37112</v>
+      </c>
+      <c r="R293" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 本宮南変電所</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="n">
@@ -18870,9 +20502,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P294" s="5" t="n"/>
-      <c r="Q294" s="5" t="n"/>
-      <c r="R294" s="5" t="n"/>
+      <c r="P294" s="5" t="n">
+        <v>37.462252</v>
+      </c>
+      <c r="Q294" s="5" t="n">
+        <v>139.006396</v>
+      </c>
+      <c r="R294" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 東栃尾変電所</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="3" t="n">
@@ -18934,9 +20574,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P295" s="5" t="n"/>
-      <c r="Q295" s="5" t="n"/>
-      <c r="R295" s="5" t="n"/>
+      <c r="P295" s="5" t="n">
+        <v>37.176342</v>
+      </c>
+      <c r="Q295" s="5" t="n">
+        <v>138.267658</v>
+      </c>
+      <c r="R295" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 東直江津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="n">
@@ -18998,9 +20646,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P296" s="5" t="n"/>
-      <c r="Q296" s="5" t="n"/>
-      <c r="R296" s="5" t="n"/>
+      <c r="P296" s="5" t="n">
+        <v>37.128896</v>
+      </c>
+      <c r="Q296" s="5" t="n">
+        <v>138.606417</v>
+      </c>
+      <c r="R296" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 松代変電所</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="n">
@@ -19062,9 +20718,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P297" s="5" t="n"/>
-      <c r="Q297" s="5" t="n"/>
-      <c r="R297" s="5" t="n"/>
+      <c r="P297" s="5" t="n">
+        <v>37.908294</v>
+      </c>
+      <c r="Q297" s="5" t="n">
+        <v>139.337955</v>
+      </c>
+      <c r="R297" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 松浦変電所</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="n">
@@ -19190,9 +20854,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P299" s="5" t="n"/>
-      <c r="Q299" s="5" t="n"/>
-      <c r="R299" s="5" t="n"/>
+      <c r="P299" s="5" t="n">
+        <v>37.575782</v>
+      </c>
+      <c r="Q299" s="5" t="n">
+        <v>139.922851</v>
+      </c>
+      <c r="R299" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 河東変電所</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="n">
@@ -19254,9 +20926,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P300" s="5" t="n"/>
-      <c r="Q300" s="5" t="n"/>
-      <c r="R300" s="5" t="n"/>
+      <c r="P300" s="5" t="n">
+        <v>37.214068</v>
+      </c>
+      <c r="Q300" s="5" t="n">
+        <v>138.32925</v>
+      </c>
+      <c r="R300" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 潟町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="n">
@@ -19318,9 +20998,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P301" s="5" t="n"/>
-      <c r="Q301" s="5" t="n"/>
-      <c r="R301" s="5" t="n"/>
+      <c r="P301" s="5" t="n">
+        <v>37.024398</v>
+      </c>
+      <c r="Q301" s="5" t="n">
+        <v>137.815359</v>
+      </c>
+      <c r="R301" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク（株）田海変電所</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="3" t="n">
@@ -19382,9 +21070,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P302" s="5" t="n"/>
-      <c r="Q302" s="5" t="n"/>
-      <c r="R302" s="5" t="n"/>
+      <c r="P302" s="5" t="n">
+        <v>38.017343</v>
+      </c>
+      <c r="Q302" s="5" t="n">
+        <v>140.143797</v>
+      </c>
+      <c r="R302" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 石岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="3" t="n">
@@ -19446,9 +21142,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P303" s="5" t="n"/>
-      <c r="Q303" s="5" t="n"/>
-      <c r="R303" s="5" t="n"/>
+      <c r="P303" s="5" t="n">
+        <v>36.973485</v>
+      </c>
+      <c r="Q303" s="5" t="n">
+        <v>138.803266</v>
+      </c>
+      <c r="R303" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 石打変電所</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="3" t="n">
@@ -19510,9 +21214,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P304" s="5" t="n"/>
-      <c r="Q304" s="5" t="n"/>
-      <c r="R304" s="5" t="n"/>
+      <c r="P304" s="5" t="n">
+        <v>38.204718</v>
+      </c>
+      <c r="Q304" s="5" t="n">
+        <v>139.450385</v>
+      </c>
+      <c r="R304" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 神林変電所</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="3" t="n">
@@ -19574,9 +21286,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P305" s="5" t="n"/>
-      <c r="Q305" s="5" t="n"/>
-      <c r="R305" s="5" t="n"/>
+      <c r="P305" s="5" t="n">
+        <v>37.965195</v>
+      </c>
+      <c r="Q305" s="5" t="n">
+        <v>140.123699</v>
+      </c>
+      <c r="R305" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株)窪田町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="3" t="n">
@@ -19638,9 +21358,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P306" s="5" t="n"/>
-      <c r="Q306" s="5" t="n"/>
-      <c r="R306" s="5" t="n"/>
+      <c r="P306" s="5" t="n">
+        <v>37.253684</v>
+      </c>
+      <c r="Q306" s="5" t="n">
+        <v>140.071437</v>
+      </c>
+      <c r="R306" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 羽鳥変電所</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="3" t="n">
@@ -19702,9 +21430,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P307" s="5" t="n"/>
-      <c r="Q307" s="5" t="n"/>
-      <c r="R307" s="5" t="n"/>
+      <c r="P307" s="5" t="n">
+        <v>37.430659</v>
+      </c>
+      <c r="Q307" s="5" t="n">
+        <v>140.58722</v>
+      </c>
+      <c r="R307" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 船引変電所</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="n">
@@ -19766,9 +21502,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P308" s="5" t="n"/>
-      <c r="Q308" s="5" t="n"/>
-      <c r="R308" s="5" t="n"/>
+      <c r="P308" s="5" t="n">
+        <v>38.117107</v>
+      </c>
+      <c r="Q308" s="5" t="n">
+        <v>139.461089</v>
+      </c>
+      <c r="R308" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 荒川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="3" t="n">
@@ -19830,9 +21574,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P309" s="5" t="n"/>
-      <c r="Q309" s="5" t="n"/>
-      <c r="R309" s="5" t="n"/>
+      <c r="P309" s="5" t="n">
+        <v>37.15765</v>
+      </c>
+      <c r="Q309" s="5" t="n">
+        <v>138.443573</v>
+      </c>
+      <c r="R309" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク（株）虫川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="3" t="n">
@@ -19894,9 +21646,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P310" s="5" t="n"/>
-      <c r="Q310" s="5" t="n"/>
-      <c r="R310" s="5" t="n"/>
+      <c r="P310" s="5" t="n">
+        <v>39.195695</v>
+      </c>
+      <c r="Q310" s="5" t="n">
+        <v>140.390359</v>
+      </c>
+      <c r="R310" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 西馬音内変電所</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="3" t="n">
@@ -19958,9 +21718,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P311" s="5" t="n"/>
-      <c r="Q311" s="5" t="n"/>
-      <c r="R311" s="5" t="n"/>
+      <c r="P311" s="5" t="n">
+        <v>38.721979</v>
+      </c>
+      <c r="Q311" s="5" t="n">
+        <v>139.802268</v>
+      </c>
+      <c r="R311" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 西鶴岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="3" t="n">
@@ -20022,9 +21790,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P312" s="5" t="n"/>
-      <c r="Q312" s="5" t="n"/>
-      <c r="R312" s="5" t="n"/>
+      <c r="P312" s="5" t="n">
+        <v>36.92502</v>
+      </c>
+      <c r="Q312" s="5" t="n">
+        <v>138.842652</v>
+      </c>
+      <c r="R312" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株)越後中里変電所</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="n">
@@ -20086,9 +21862,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P313" s="5" t="n"/>
-      <c r="Q313" s="5" t="n"/>
-      <c r="R313" s="5" t="n"/>
+      <c r="P313" s="5" t="n">
+        <v>38.338484</v>
+      </c>
+      <c r="Q313" s="5" t="n">
+        <v>140.292043</v>
+      </c>
+      <c r="R313" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 長崎変電所</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="3" t="n">
@@ -20150,9 +21934,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P314" s="5" t="n"/>
-      <c r="Q314" s="5" t="n"/>
-      <c r="R314" s="5" t="n"/>
+      <c r="P314" s="5" t="n">
+        <v>37.456817</v>
+      </c>
+      <c r="Q314" s="5" t="n">
+        <v>139.912407</v>
+      </c>
+      <c r="R314" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株)門田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="3" t="n">
@@ -20214,9 +22006,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P315" s="5" t="n"/>
-      <c r="Q315" s="5" t="n"/>
-      <c r="R315" s="5" t="n"/>
+      <c r="P315" s="5" t="n">
+        <v>36.921385</v>
+      </c>
+      <c r="Q315" s="5" t="n">
+        <v>138.224631</v>
+      </c>
+      <c r="R315" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク(株) 関山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="3" t="n">
@@ -20278,9 +22078,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P316" s="5" t="n"/>
-      <c r="Q316" s="5" t="n"/>
-      <c r="R316" s="5" t="n"/>
+      <c r="P316" s="5" t="n">
+        <v>38.794062</v>
+      </c>
+      <c r="Q316" s="5" t="n">
+        <v>140.656436</v>
+      </c>
+      <c r="R316" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 東北電力ネットワーク㈱ 鬼首変電所</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="3" t="n">
@@ -20344,9 +22152,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P317" s="5" t="n"/>
-      <c r="Q317" s="5" t="n"/>
-      <c r="R317" s="5" t="n"/>
+      <c r="P317" s="5" t="n">
+        <v>34.391258</v>
+      </c>
+      <c r="Q317" s="5" t="n">
+        <v>133.054359</v>
+      </c>
+      <c r="R317" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 中国電力ネットワーク(株) 三原変電所</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="3" t="n">
@@ -20410,9 +22226,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P318" s="5" t="n"/>
-      <c r="Q318" s="5" t="n"/>
-      <c r="R318" s="5" t="n"/>
+      <c r="P318" s="5" t="n">
+        <v>34.667078</v>
+      </c>
+      <c r="Q318" s="5" t="n">
+        <v>133.680206</v>
+      </c>
+      <c r="R318" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 久代変電所</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="3" t="n">
@@ -20476,9 +22300,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P319" s="5" t="n"/>
-      <c r="Q319" s="5" t="n"/>
-      <c r="R319" s="5" t="n"/>
+      <c r="P319" s="5" t="n">
+        <v>34.58068</v>
+      </c>
+      <c r="Q319" s="5" t="n">
+        <v>133.229999</v>
+      </c>
+      <c r="R319" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 出口変電所</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="3" t="n">
@@ -20608,9 +22440,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P321" s="5" t="n"/>
-      <c r="Q321" s="5" t="n"/>
-      <c r="R321" s="5" t="n"/>
+      <c r="P321" s="5" t="n">
+        <v>34.535632</v>
+      </c>
+      <c r="Q321" s="5" t="n">
+        <v>133.342152</v>
+      </c>
+      <c r="R321" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 御幸変電所</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="3" t="n">
@@ -20674,9 +22514,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P322" s="5" t="n"/>
-      <c r="Q322" s="5" t="n"/>
-      <c r="R322" s="5" t="n"/>
+      <c r="P322" s="5" t="n">
+        <v>34.478972</v>
+      </c>
+      <c r="Q322" s="5" t="n">
+        <v>133.379649</v>
+      </c>
+      <c r="R322" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 松浜変電所</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="n">
@@ -20740,9 +22588,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P323" s="5" t="n"/>
-      <c r="Q323" s="5" t="n"/>
-      <c r="R323" s="5" t="n"/>
+      <c r="P323" s="5" t="n">
+        <v>34.469424</v>
+      </c>
+      <c r="Q323" s="5" t="n">
+        <v>133.31404</v>
+      </c>
+      <c r="R323" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 瀬戸変電所</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="3" t="n">
@@ -20806,9 +22662,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P324" s="5" t="n"/>
-      <c r="Q324" s="5" t="n"/>
-      <c r="R324" s="5" t="n"/>
+      <c r="P324" s="5" t="n">
+        <v>34.576263</v>
+      </c>
+      <c r="Q324" s="5" t="n">
+        <v>133.693048</v>
+      </c>
+      <c r="R324" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 船穂変電所</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="3" t="n">
@@ -20872,9 +22736,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P325" s="5" t="n"/>
-      <c r="Q325" s="5" t="n"/>
-      <c r="R325" s="5" t="n"/>
+      <c r="P325" s="5" t="n">
+        <v>34.574834</v>
+      </c>
+      <c r="Q325" s="5" t="n">
+        <v>133.32972</v>
+      </c>
+      <c r="R325" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 駅家北変電所</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="3" t="n">
@@ -20996,9 +22868,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P327" s="5" t="n"/>
-      <c r="Q327" s="5" t="n"/>
-      <c r="R327" s="5" t="n"/>
+      <c r="P327" s="5" t="n">
+        <v>35.007949</v>
+      </c>
+      <c r="Q327" s="5" t="n">
+        <v>135.764336</v>
+      </c>
+      <c r="R327" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱三条変電所</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="3" t="n">
@@ -21306,9 +23186,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P332" s="5" t="n"/>
-      <c r="Q332" s="5" t="n"/>
-      <c r="R332" s="5" t="n"/>
+      <c r="P332" s="5" t="n">
+        <v>35.651675</v>
+      </c>
+      <c r="Q332" s="5" t="n">
+        <v>134.970081</v>
+      </c>
+      <c r="R332" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力株式会社 丹後木津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="3" t="n">
@@ -21492,9 +23380,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P335" s="5" t="n"/>
-      <c r="Q335" s="5" t="n"/>
-      <c r="R335" s="5" t="n"/>
+      <c r="P335" s="5" t="n">
+        <v>34.49067</v>
+      </c>
+      <c r="Q335" s="5" t="n">
+        <v>135.477143</v>
+      </c>
+      <c r="R335" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力光明池変電所</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="3" t="n">
@@ -21554,9 +23450,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P336" s="5" t="n"/>
-      <c r="Q336" s="5" t="n"/>
-      <c r="R336" s="5" t="n"/>
+      <c r="P336" s="5" t="n">
+        <v>34.800512</v>
+      </c>
+      <c r="Q336" s="5" t="n">
+        <v>135.452759</v>
+      </c>
+      <c r="R336" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力刀根山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="3" t="n">
@@ -21740,9 +23644,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P339" s="5" t="n"/>
-      <c r="Q339" s="5" t="n"/>
-      <c r="R339" s="5" t="n"/>
+      <c r="P339" s="5" t="n">
+        <v>34.963934</v>
+      </c>
+      <c r="Q339" s="5" t="n">
+        <v>135.679061</v>
+      </c>
+      <c r="R339" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 大原野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="3" t="n">
@@ -21802,9 +23714,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P340" s="5" t="n"/>
-      <c r="Q340" s="5" t="n"/>
-      <c r="R340" s="5" t="n"/>
+      <c r="P340" s="5" t="n">
+        <v>34.688805</v>
+      </c>
+      <c r="Q340" s="5" t="n">
+        <v>135.512598</v>
+      </c>
+      <c r="R340" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電天満橋変電所</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="3" t="n">
@@ -21988,9 +23908,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P343" s="5" t="n"/>
-      <c r="Q343" s="5" t="n"/>
-      <c r="R343" s="5" t="n"/>
+      <c r="P343" s="5" t="n">
+        <v>34.724239</v>
+      </c>
+      <c r="Q343" s="5" t="n">
+        <v>135.828532</v>
+      </c>
+      <c r="R343" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 学研木津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="3" t="n">
@@ -22112,9 +24040,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P345" s="5" t="n"/>
-      <c r="Q345" s="5" t="n"/>
-      <c r="R345" s="5" t="n"/>
+      <c r="P345" s="5" t="n">
+        <v>34.725715</v>
+      </c>
+      <c r="Q345" s="5" t="n">
+        <v>135.57685</v>
+      </c>
+      <c r="R345" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 寺方変電所</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="3" t="n">
@@ -22174,9 +24110,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P346" s="5" t="n"/>
-      <c r="Q346" s="5" t="n"/>
-      <c r="R346" s="5" t="n"/>
+      <c r="P346" s="5" t="n">
+        <v>34.904476</v>
+      </c>
+      <c r="Q346" s="5" t="n">
+        <v>135.78331</v>
+      </c>
+      <c r="R346" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱ 小倉変電所</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="3" t="n">
@@ -22298,9 +24242,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P348" s="5" t="n"/>
-      <c r="Q348" s="5" t="n"/>
-      <c r="R348" s="5" t="n"/>
+      <c r="P348" s="5" t="n">
+        <v>34.986585</v>
+      </c>
+      <c r="Q348" s="5" t="n">
+        <v>135.817121</v>
+      </c>
+      <c r="R348" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 山科変電所</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="3" t="n">
@@ -22360,9 +24312,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P349" s="5" t="n"/>
-      <c r="Q349" s="5" t="n"/>
-      <c r="R349" s="5" t="n"/>
+      <c r="P349" s="5" t="n">
+        <v>34.252155</v>
+      </c>
+      <c r="Q349" s="5" t="n">
+        <v>135.318905</v>
+      </c>
+      <c r="R349" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱岩出変電所</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="3" t="n">
@@ -22422,9 +24382,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P350" s="5" t="n"/>
-      <c r="Q350" s="5" t="n"/>
-      <c r="R350" s="5" t="n"/>
+      <c r="P350" s="5" t="n">
+        <v>35.575356</v>
+      </c>
+      <c r="Q350" s="5" t="n">
+        <v>135.160003</v>
+      </c>
+      <c r="R350" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 岩滝変電所</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="3" t="n">
@@ -22484,9 +24452,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P351" s="5" t="n"/>
-      <c r="Q351" s="5" t="n"/>
-      <c r="R351" s="5" t="n"/>
+      <c r="P351" s="5" t="n">
+        <v>34.465574</v>
+      </c>
+      <c r="Q351" s="5" t="n">
+        <v>135.389093</v>
+      </c>
+      <c r="R351" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱岸和田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="3" t="n">
@@ -22546,9 +24522,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P352" s="5" t="n"/>
-      <c r="Q352" s="5" t="n"/>
-      <c r="R352" s="5" t="n"/>
+      <c r="P352" s="5" t="n">
+        <v>34.63674</v>
+      </c>
+      <c r="Q352" s="5" t="n">
+        <v>135.550724</v>
+      </c>
+      <c r="R352" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力㈱巽変電所</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="3" t="n">
@@ -22670,9 +24654,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P354" s="5" t="n"/>
-      <c r="Q354" s="5" t="n"/>
-      <c r="R354" s="5" t="n"/>
+      <c r="P354" s="5" t="n">
+        <v>34.626697</v>
+      </c>
+      <c r="Q354" s="5" t="n">
+        <v>135.572754</v>
+      </c>
+      <c r="R354" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 平野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="3" t="n">
@@ -22918,9 +24910,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P358" s="5" t="n"/>
-      <c r="Q358" s="5" t="n"/>
-      <c r="R358" s="5" t="n"/>
+      <c r="P358" s="5" t="n">
+        <v>34.987376</v>
+      </c>
+      <c r="Q358" s="5" t="n">
+        <v>135.982103</v>
+      </c>
+      <c r="R358" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 志津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="3" t="n">
@@ -23042,9 +25042,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P360" s="5" t="n"/>
-      <c r="Q360" s="5" t="n"/>
-      <c r="R360" s="5" t="n"/>
+      <c r="P360" s="5" t="n">
+        <v>34.841667</v>
+      </c>
+      <c r="Q360" s="5" t="n">
+        <v>135.636861</v>
+      </c>
+      <c r="R360" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 東天川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="3" t="n">
@@ -23104,9 +25112,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P361" s="5" t="n"/>
-      <c r="Q361" s="5" t="n"/>
-      <c r="R361" s="5" t="n"/>
+      <c r="P361" s="5" t="n">
+        <v>34.737075</v>
+      </c>
+      <c r="Q361" s="5" t="n">
+        <v>135.502192</v>
+      </c>
+      <c r="R361" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電 東淀川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="3" t="n">
@@ -23352,9 +25368,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P365" s="5" t="n"/>
-      <c r="Q365" s="5" t="n"/>
-      <c r="R365" s="5" t="n"/>
+      <c r="P365" s="5" t="n">
+        <v>34.719112</v>
+      </c>
+      <c r="Q365" s="5" t="n">
+        <v>135.55086</v>
+      </c>
+      <c r="R365" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 森小路変電所</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="3" t="n">
@@ -23538,9 +25562,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P368" s="5" t="n"/>
-      <c r="Q368" s="5" t="n"/>
-      <c r="R368" s="5" t="n"/>
+      <c r="P368" s="5" t="n">
+        <v>34.667715</v>
+      </c>
+      <c r="Q368" s="5" t="n">
+        <v>135.572491</v>
+      </c>
+      <c r="R368" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 永和変電所</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="3" t="n">
@@ -23600,9 +25632,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P369" s="5" t="n"/>
-      <c r="Q369" s="5" t="n"/>
-      <c r="R369" s="5" t="n"/>
+      <c r="P369" s="5" t="n">
+        <v>34.788687</v>
+      </c>
+      <c r="Q369" s="5" t="n">
+        <v>135.575428</v>
+      </c>
+      <c r="R369" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沢良宜変電所</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="3" t="n">
@@ -23662,9 +25702,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P370" s="5" t="n"/>
-      <c r="Q370" s="5" t="n"/>
-      <c r="R370" s="5" t="n"/>
+      <c r="P370" s="5" t="n">
+        <v>34.50237</v>
+      </c>
+      <c r="Q370" s="5" t="n">
+        <v>135.411816</v>
+      </c>
+      <c r="R370" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱泉大津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="3" t="n">
@@ -23724,9 +25772,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P371" s="5" t="n"/>
-      <c r="Q371" s="5" t="n"/>
-      <c r="R371" s="5" t="n"/>
+      <c r="P371" s="5" t="n">
+        <v>34.655869</v>
+      </c>
+      <c r="Q371" s="5" t="n">
+        <v>135.633183</v>
+      </c>
+      <c r="R371" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 瓢箪山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="3" t="n">
@@ -23910,9 +25966,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P374" s="5" t="n"/>
-      <c r="Q374" s="5" t="n"/>
-      <c r="R374" s="5" t="n"/>
+      <c r="P374" s="5" t="n">
+        <v>34.819826</v>
+      </c>
+      <c r="Q374" s="5" t="n">
+        <v>135.652929</v>
+      </c>
+      <c r="R374" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 禁野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="3" t="n">
@@ -24034,9 +26098,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P376" s="5" t="n"/>
-      <c r="Q376" s="5" t="n"/>
-      <c r="R376" s="5" t="n"/>
+      <c r="P376" s="5" t="n">
+        <v>34.678801</v>
+      </c>
+      <c r="Q376" s="5" t="n">
+        <v>135.488333</v>
+      </c>
+      <c r="R376" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力立売堀変電所</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="3" t="n">
@@ -24220,9 +26292,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P379" s="5" t="n"/>
-      <c r="Q379" s="5" t="n"/>
-      <c r="R379" s="5" t="n"/>
+      <c r="P379" s="5" t="n">
+        <v>34.548068</v>
+      </c>
+      <c r="Q379" s="5" t="n">
+        <v>135.553703</v>
+      </c>
+      <c r="R379" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 美原変電所</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="3" t="n">
@@ -24282,9 +26362,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P380" s="5" t="n"/>
-      <c r="Q380" s="5" t="n"/>
-      <c r="R380" s="5" t="n"/>
+      <c r="P380" s="5" t="n">
+        <v>34.609104</v>
+      </c>
+      <c r="Q380" s="5" t="n">
+        <v>135.592872</v>
+      </c>
+      <c r="R380" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱老原変電所</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="3" t="n">
@@ -24406,9 +26494,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P382" s="5" t="n"/>
-      <c r="Q382" s="5" t="n"/>
-      <c r="R382" s="5" t="n"/>
+      <c r="P382" s="5" t="n">
+        <v>34.685817</v>
+      </c>
+      <c r="Q382" s="5" t="n">
+        <v>135.507635</v>
+      </c>
+      <c r="R382" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力船場変電所</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="3" t="n">
@@ -24468,9 +26564,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P383" s="5" t="n"/>
-      <c r="Q383" s="5" t="n"/>
-      <c r="R383" s="5" t="n"/>
+      <c r="P383" s="5" t="n">
+        <v>34.657828</v>
+      </c>
+      <c r="Q383" s="5" t="n">
+        <v>135.612315</v>
+      </c>
+      <c r="R383" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電花園変電所</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="3" t="n">
@@ -24530,9 +26634,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P384" s="5" t="n"/>
-      <c r="Q384" s="5" t="n"/>
-      <c r="R384" s="5" t="n"/>
+      <c r="P384" s="5" t="n">
+        <v>34.602545</v>
+      </c>
+      <c r="Q384" s="5" t="n">
+        <v>135.521427</v>
+      </c>
+      <c r="R384" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 苅田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="3" t="n">
@@ -24592,9 +26704,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P385" s="5" t="n"/>
-      <c r="Q385" s="5" t="n"/>
-      <c r="R385" s="5" t="n"/>
+      <c r="P385" s="5" t="n">
+        <v>35.018896</v>
+      </c>
+      <c r="Q385" s="5" t="n">
+        <v>135.965266</v>
+      </c>
+      <c r="R385" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電草津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="3" t="n">
@@ -24716,9 +26836,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P387" s="5" t="n"/>
-      <c r="Q387" s="5" t="n"/>
-      <c r="R387" s="5" t="n"/>
+      <c r="P387" s="5" t="n">
+        <v>34.987072</v>
+      </c>
+      <c r="Q387" s="5" t="n">
+        <v>135.721394</v>
+      </c>
+      <c r="R387" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 西京極変電所</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="3" t="n">
@@ -24778,9 +26906,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P388" s="5" t="n"/>
-      <c r="Q388" s="5" t="n"/>
-      <c r="R388" s="5" t="n"/>
+      <c r="P388" s="5" t="n">
+        <v>34.63139</v>
+      </c>
+      <c r="Q388" s="5" t="n">
+        <v>135.587607</v>
+      </c>
+      <c r="R388" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 西八尾変電所</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="3" t="n">
@@ -24840,9 +26976,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P389" s="5" t="n"/>
-      <c r="Q389" s="5" t="n"/>
-      <c r="R389" s="5" t="n"/>
+      <c r="P389" s="5" t="n">
+        <v>34.67586</v>
+      </c>
+      <c r="Q389" s="5" t="n">
+        <v>135.578027</v>
+      </c>
+      <c r="R389" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力西堤変電所</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="3" t="n">
@@ -25026,9 +27170,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P392" s="5" t="n"/>
-      <c r="Q392" s="5" t="n"/>
-      <c r="R392" s="5" t="n"/>
+      <c r="P392" s="5" t="n">
+        <v>35.005296</v>
+      </c>
+      <c r="Q392" s="5" t="n">
+        <v>135.754727</v>
+      </c>
+      <c r="R392" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 錦変電所</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="3" t="n">
@@ -25150,9 +27302,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P394" s="5" t="n"/>
-      <c r="Q394" s="5" t="n"/>
-      <c r="R394" s="5" t="n"/>
+      <c r="P394" s="5" t="n">
+        <v>34.711868</v>
+      </c>
+      <c r="Q394" s="5" t="n">
+        <v>135.512618</v>
+      </c>
+      <c r="R394" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱長柄変電所</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="3" t="n">
@@ -25212,9 +27372,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P395" s="5" t="n"/>
-      <c r="Q395" s="5" t="n"/>
-      <c r="R395" s="5" t="n"/>
+      <c r="P395" s="5" t="n">
+        <v>34.382351</v>
+      </c>
+      <c r="Q395" s="5" t="n">
+        <v>135.315891</v>
+      </c>
+      <c r="R395" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力送配電㈱長滝変電所</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="3" t="n">
@@ -25336,9 +27504,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P397" s="5" t="n"/>
-      <c r="Q397" s="5" t="n"/>
-      <c r="R397" s="5" t="n"/>
+      <c r="P397" s="5" t="n">
+        <v>34.705747</v>
+      </c>
+      <c r="Q397" s="5" t="n">
+        <v>135.552376</v>
+      </c>
+      <c r="R397" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力関目変電所</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="3" t="n">
@@ -25398,9 +27574,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P398" s="5" t="n"/>
-      <c r="Q398" s="5" t="n"/>
-      <c r="R398" s="5" t="n"/>
+      <c r="P398" s="5" t="n">
+        <v>34.851911</v>
+      </c>
+      <c r="Q398" s="5" t="n">
+        <v>135.591413</v>
+      </c>
+      <c r="R398" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 阿武野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="3" t="n">
@@ -25646,9 +27830,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P402" s="5" t="n"/>
-      <c r="Q402" s="5" t="n"/>
-      <c r="R402" s="5" t="n"/>
+      <c r="P402" s="5" t="n">
+        <v>34.303091</v>
+      </c>
+      <c r="Q402" s="5" t="n">
+        <v>135.564654</v>
+      </c>
+      <c r="R402" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 高野口変電所</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="3" t="n">
@@ -25708,9 +27900,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P403" s="5" t="n"/>
-      <c r="Q403" s="5" t="n"/>
-      <c r="R403" s="5" t="n"/>
+      <c r="P403" s="5" t="n">
+        <v>34.612982</v>
+      </c>
+      <c r="Q403" s="5" t="n">
+        <v>135.527235</v>
+      </c>
+      <c r="R403" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 関西電力鷹合町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="3" t="n">
@@ -25772,9 +27972,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P404" s="5" t="n"/>
-      <c r="Q404" s="5" t="n"/>
-      <c r="R404" s="5" t="n"/>
+      <c r="P404" s="5" t="n">
+        <v>26.657201</v>
+      </c>
+      <c r="Q404" s="5" t="n">
+        <v>127.906535</v>
+      </c>
+      <c r="R404" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力（株）本部変電所</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="3" t="n">
@@ -25832,9 +28040,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P405" s="5" t="n"/>
-      <c r="Q405" s="5" t="n"/>
-      <c r="R405" s="5" t="n"/>
+      <c r="P405" s="5" t="n">
+        <v>26.153804</v>
+      </c>
+      <c r="Q405" s="5" t="n">
+        <v>127.673144</v>
+      </c>
+      <c r="R405" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 沖縄電力 阿波根変電所</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="3" t="n">
@@ -25898,9 +28114,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P406" s="5" t="n"/>
-      <c r="Q406" s="5" t="n"/>
-      <c r="R406" s="5" t="n"/>
+      <c r="P406" s="5" t="n">
+        <v>34.425444</v>
+      </c>
+      <c r="Q406" s="5" t="n">
+        <v>133.233454</v>
+      </c>
+      <c r="R406" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 高須変電所</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="3" t="n">
@@ -26631,9 +28855,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P3" s="5" t="n"/>
-      <c r="Q3" s="5" t="n"/>
-      <c r="R3" s="5" t="n"/>
+      <c r="P3" s="5" t="n">
+        <v>35.624718</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>136.056254</v>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 南敦賀変電所</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -26695,9 +28927,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="n"/>
-      <c r="R4" s="5" t="n"/>
+      <c r="P4" s="5" t="n">
+        <v>36.559793</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>136.64532</v>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 増泉変電所</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -26759,9 +28999,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
+      <c r="P5" s="5" t="n">
+        <v>36.558955</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>136.653305</v>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 大工町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -26823,9 +29071,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
+      <c r="P6" s="5" t="n">
+        <v>36.046304</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>136.254138</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 成和変電所</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -26887,9 +29143,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
+      <c r="P7" s="5" t="n">
+        <v>36.574655</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>136.646673</v>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 昭和町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -26951,9 +29215,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
+      <c r="P8" s="5" t="n">
+        <v>36.546242</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>136.649333</v>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 泉野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -27015,9 +29287,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
+      <c r="P9" s="5" t="n">
+        <v>36.548498</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>136.556799</v>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 竹松変電所</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -27143,9 +29423,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
+      <c r="P11" s="5" t="n">
+        <v>36.072493</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>136.476229</v>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 荒土変電所</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -27207,9 +29495,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
+      <c r="P12" s="5" t="n">
+        <v>36.568186</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>136.661086</v>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 金沢中央変電所</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -27271,9 +29567,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
+      <c r="P13" s="5" t="n">
+        <v>36.604579</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>136.601017</v>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 金石変電所</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -27335,9 +29639,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
+      <c r="P14" s="5" t="n">
+        <v>36.5976</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>136.61902</v>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 鞍月変電所</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -27399,9 +29711,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
+      <c r="P15" s="5" t="n">
+        <v>34.348752</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>134.053972</v>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 丸の内変電所</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -27463,9 +29783,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
+      <c r="P16" s="5" t="n">
+        <v>34.123758</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>134.577533</v>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 今切変電所</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -27527,9 +29855,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
+      <c r="P17" s="5" t="n">
+        <v>34.082395</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>134.561043</v>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 助任変電所</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -27591,9 +29927,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
+      <c r="P18" s="5" t="n">
+        <v>33.899683</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>132.73038</v>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 勝岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -27655,9 +29999,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
+      <c r="P19" s="5" t="n">
+        <v>34.230984</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>133.789442</v>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 善通寺変電所</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -27719,9 +30071,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
+      <c r="P20" s="5" t="n">
+        <v>33.965067</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>133.518512</v>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱寒川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -27783,9 +30143,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
+      <c r="P21" s="5" t="n">
+        <v>34.133481</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>133.68511</v>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電（株）常磐変電所</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -27847,9 +30215,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
+      <c r="P22" s="5" t="n">
+        <v>33.883546</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>132.752309</v>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 平田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -27911,9 +30287,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
+      <c r="P23" s="5" t="n">
+        <v>33.554348</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>133.509035</v>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱旭変電所</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -28039,9 +30423,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
+      <c r="P25" s="5" t="n">
+        <v>33.54092</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>133.471831</v>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 朝倉変電所</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -28103,9 +30495,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
+      <c r="P26" s="5" t="n">
+        <v>33.558856</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>133.533573</v>
+      </c>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱本町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -28359,9 +30759,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="5" t="n"/>
+      <c r="P30" s="5" t="n">
+        <v>33.835097</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>132.786258</v>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 枝松変電所</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -28487,9 +30895,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="5" t="n"/>
-      <c r="R32" s="5" t="n"/>
+      <c r="P32" s="5" t="n">
+        <v>33.571527</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>133.538115</v>
+      </c>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱江の口変電所</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -28551,9 +30967,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
+      <c r="P33" s="5" t="n">
+        <v>34.008062</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>133.562849</v>
+      </c>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 浜田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -28615,9 +31039,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="5" t="n"/>
+      <c r="P34" s="5" t="n">
+        <v>33.839551</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>132.767208</v>
+      </c>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力番町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -28679,9 +31111,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="n"/>
+      <c r="P35" s="5" t="n">
+        <v>33.821306</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>132.776947</v>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 石井変電所</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -28743,9 +31183,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="5" t="n"/>
-      <c r="R36" s="5" t="n"/>
+      <c r="P36" s="5" t="n">
+        <v>33.835103</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>132.751765</v>
+      </c>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 竹原変電所</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -28807,9 +31255,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P37" s="5" t="n"/>
-      <c r="Q37" s="5" t="n"/>
-      <c r="R37" s="5" t="n"/>
+      <c r="P37" s="5" t="n">
+        <v>33.551232</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>133.532343</v>
+      </c>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 筆山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -28935,9 +31391,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P39" s="5" t="n"/>
-      <c r="Q39" s="5" t="n"/>
-      <c r="R39" s="5" t="n"/>
+      <c r="P39" s="5" t="n">
+        <v>34.34501</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>134.039453</v>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力西通変電所</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -28999,9 +31463,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P40" s="5" t="n"/>
-      <c r="Q40" s="5" t="n"/>
-      <c r="R40" s="5" t="n"/>
+      <c r="P40" s="5" t="n">
+        <v>33.851756</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>132.778966</v>
+      </c>
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 道後変電所</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -29063,9 +31535,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P41" s="5" t="n"/>
-      <c r="Q41" s="5" t="n"/>
-      <c r="R41" s="5" t="n"/>
+      <c r="P41" s="5" t="n">
+        <v>33.761802</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>132.707096</v>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱郡中変電所</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -29255,9 +31735,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P44" s="5" t="n"/>
-      <c r="Q44" s="5" t="n"/>
-      <c r="R44" s="5" t="n"/>
+      <c r="P44" s="5" t="n">
+        <v>36.696651</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>137.218486</v>
+      </c>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 中富山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -29319,9 +31807,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P45" s="5" t="n"/>
-      <c r="Q45" s="5" t="n"/>
-      <c r="R45" s="5" t="n"/>
+      <c r="P45" s="5" t="n">
+        <v>36.062864</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>136.213069</v>
+      </c>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 中福井変電所</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -29383,9 +31879,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P46" s="5" t="n"/>
-      <c r="Q46" s="5" t="n"/>
-      <c r="R46" s="5" t="n"/>
+      <c r="P46" s="5" t="n">
+        <v>36.943637</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>137.504105</v>
+      </c>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 入善変電所</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -29447,9 +31951,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P47" s="5" t="n"/>
-      <c r="Q47" s="5" t="n"/>
-      <c r="R47" s="5" t="n"/>
+      <c r="P47" s="5" t="n">
+        <v>36.729956</v>
+      </c>
+      <c r="Q47" s="5" t="n">
+        <v>137.007922</v>
+      </c>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 南高岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -29511,9 +32023,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P48" s="5" t="n"/>
-      <c r="Q48" s="5" t="n"/>
-      <c r="R48" s="5" t="n"/>
+      <c r="P48" s="5" t="n">
+        <v>36.687077</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>137.217063</v>
+      </c>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力城南変電所</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -29575,9 +32095,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P49" s="5" t="n"/>
-      <c r="Q49" s="5" t="n"/>
-      <c r="R49" s="5" t="n"/>
+      <c r="P49" s="5" t="n">
+        <v>36.70472</v>
+      </c>
+      <c r="Q49" s="5" t="n">
+        <v>137.230442</v>
+      </c>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 奥田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -29639,9 +32167,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P50" s="5" t="n"/>
-      <c r="Q50" s="5" t="n"/>
-      <c r="R50" s="5" t="n"/>
+      <c r="P50" s="5" t="n">
+        <v>36.709676</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>137.245351</v>
+      </c>
+      <c r="R50" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 広田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -29703,9 +32239,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P51" s="5" t="n"/>
-      <c r="Q51" s="5" t="n"/>
-      <c r="R51" s="5" t="n"/>
+      <c r="P51" s="5" t="n">
+        <v>36.06873</v>
+      </c>
+      <c r="Q51" s="5" t="n">
+        <v>136.215657</v>
+      </c>
+      <c r="R51" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 春山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -29767,9 +32311,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P52" s="5" t="n"/>
-      <c r="Q52" s="5" t="n"/>
-      <c r="R52" s="5" t="n"/>
+      <c r="P52" s="5" t="n">
+        <v>36.050438</v>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>136.208066</v>
+      </c>
+      <c r="R52" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 橋南変電所</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -29831,9 +32383,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P53" s="5" t="n"/>
-      <c r="Q53" s="5" t="n"/>
-      <c r="R53" s="5" t="n"/>
+      <c r="P53" s="5" t="n">
+        <v>36.706914</v>
+      </c>
+      <c r="Q53" s="5" t="n">
+        <v>137.21239</v>
+      </c>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電 牛島変電所</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -29895,9 +32455,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P54" s="5" t="n"/>
-      <c r="Q54" s="5" t="n"/>
-      <c r="R54" s="5" t="n"/>
+      <c r="P54" s="5" t="n">
+        <v>36.755262</v>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>137.006372</v>
+      </c>
+      <c r="R54" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 西高岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -29959,9 +32527,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P55" s="5" t="n"/>
-      <c r="Q55" s="5" t="n"/>
-      <c r="R55" s="5" t="n"/>
+      <c r="P55" s="5" t="n">
+        <v>33.561471</v>
+      </c>
+      <c r="Q55" s="5" t="n">
+        <v>133.565483</v>
+      </c>
+      <c r="R55" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 下知変電所</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -30023,9 +32599,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P56" s="5" t="n"/>
-      <c r="Q56" s="5" t="n"/>
-      <c r="R56" s="5" t="n"/>
+      <c r="P56" s="5" t="n">
+        <v>32.988213</v>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>132.950222</v>
+      </c>
+      <c r="R56" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 中村変電所</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -30087,9 +32671,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P57" s="5" t="n"/>
-      <c r="Q57" s="5" t="n"/>
-      <c r="R57" s="5" t="n"/>
+      <c r="P57" s="5" t="n">
+        <v>33.489831</v>
+      </c>
+      <c r="Q57" s="5" t="n">
+        <v>132.316661</v>
+      </c>
+      <c r="R57" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力（株）亀浦変電所</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -30151,9 +32743,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P58" s="5" t="n"/>
-      <c r="Q58" s="5" t="n"/>
-      <c r="R58" s="5" t="n"/>
+      <c r="P58" s="5" t="n">
+        <v>33.550976</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>133.429722</v>
+      </c>
+      <c r="R58" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 伊野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -30215,9 +32815,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P59" s="5" t="n"/>
-      <c r="Q59" s="5" t="n"/>
-      <c r="R59" s="5" t="n"/>
+      <c r="P59" s="5" t="n">
+        <v>33.486317</v>
+      </c>
+      <c r="Q59" s="5" t="n">
+        <v>132.4066</v>
+      </c>
+      <c r="R59" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 保内変電所</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -30279,9 +32887,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P60" s="5" t="n"/>
-      <c r="Q60" s="5" t="n"/>
-      <c r="R60" s="5" t="n"/>
+      <c r="P60" s="5" t="n">
+        <v>33.456995</v>
+      </c>
+      <c r="Q60" s="5" t="n">
+        <v>132.436768</v>
+      </c>
+      <c r="R60" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 八幡浜変電所</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -30343,9 +32959,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P61" s="5" t="n"/>
-      <c r="Q61" s="5" t="n"/>
-      <c r="R61" s="5" t="n"/>
+      <c r="P61" s="5" t="n">
+        <v>33.543939</v>
+      </c>
+      <c r="Q61" s="5" t="n">
+        <v>132.648976</v>
+      </c>
+      <c r="R61" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 内子変電所</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -30407,9 +33031,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P62" s="5" t="n"/>
-      <c r="Q62" s="5" t="n"/>
-      <c r="R62" s="5" t="n"/>
+      <c r="P62" s="5" t="n">
+        <v>34.324798</v>
+      </c>
+      <c r="Q62" s="5" t="n">
+        <v>133.858366</v>
+      </c>
+      <c r="R62" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱大浜変電所</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -30471,9 +33103,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P63" s="5" t="n"/>
-      <c r="Q63" s="5" t="n"/>
-      <c r="R63" s="5" t="n"/>
+      <c r="P63" s="5" t="n">
+        <v>33.231386</v>
+      </c>
+      <c r="Q63" s="5" t="n">
+        <v>132.555154</v>
+      </c>
+      <c r="R63" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 大浦変電所</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -30535,9 +33175,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P64" s="5" t="n"/>
-      <c r="Q64" s="5" t="n"/>
-      <c r="R64" s="5" t="n"/>
+      <c r="P64" s="5" t="n">
+        <v>33.291004</v>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>134.149639</v>
+      </c>
+      <c r="R64" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株)室戸変電所</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -30599,9 +33247,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P65" s="5" t="n"/>
-      <c r="Q65" s="5" t="n"/>
-      <c r="R65" s="5" t="n"/>
+      <c r="P65" s="5" t="n">
+        <v>32.934523</v>
+      </c>
+      <c r="Q65" s="5" t="n">
+        <v>132.71309</v>
+      </c>
+      <c r="R65" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 宿毛変電所</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -30663,9 +33319,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P66" s="5" t="n"/>
-      <c r="Q66" s="5" t="n"/>
-      <c r="R66" s="5" t="n"/>
+      <c r="P66" s="5" t="n">
+        <v>33.917115</v>
+      </c>
+      <c r="Q66" s="5" t="n">
+        <v>134.661134</v>
+      </c>
+      <c r="R66" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 富岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -30727,9 +33391,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P67" s="5" t="n"/>
-      <c r="Q67" s="5" t="n"/>
-      <c r="R67" s="5" t="n"/>
+      <c r="P67" s="5" t="n">
+        <v>34.004149</v>
+      </c>
+      <c r="Q67" s="5" t="n">
+        <v>134.591096</v>
+      </c>
+      <c r="R67" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱小松島変電所</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -30791,9 +33463,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P68" s="5" t="n"/>
-      <c r="Q68" s="5" t="n"/>
-      <c r="R68" s="5" t="n"/>
+      <c r="P68" s="5" t="n">
+        <v>33.209697</v>
+      </c>
+      <c r="Q68" s="5" t="n">
+        <v>132.561402</v>
+      </c>
+      <c r="R68" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 山際変電所</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -30919,9 +33599,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P70" s="5" t="n"/>
-      <c r="Q70" s="5" t="n"/>
-      <c r="R70" s="5" t="n"/>
+      <c r="P70" s="5" t="n">
+        <v>34.06561</v>
+      </c>
+      <c r="Q70" s="5" t="n">
+        <v>134.577589</v>
+      </c>
+      <c r="R70" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 末広変電所</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -30983,9 +33671,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P71" s="5" t="n"/>
-      <c r="Q71" s="5" t="n"/>
-      <c r="R71" s="5" t="n"/>
+      <c r="P71" s="5" t="n">
+        <v>33.968584</v>
+      </c>
+      <c r="Q71" s="5" t="n">
+        <v>133.296601</v>
+      </c>
+      <c r="R71" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱東雲変電所</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -31047,9 +33743,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P72" s="5" t="n"/>
-      <c r="Q72" s="5" t="n"/>
-      <c r="R72" s="5" t="n"/>
+      <c r="P72" s="5" t="n">
+        <v>34.060154</v>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>133.00985</v>
+      </c>
+      <c r="R72" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱枝堀変電所</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -31111,9 +33815,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P73" s="5" t="n"/>
-      <c r="Q73" s="5" t="n"/>
-      <c r="R73" s="5" t="n"/>
+      <c r="P73" s="5" t="n">
+        <v>34.025299</v>
+      </c>
+      <c r="Q73" s="5" t="n">
+        <v>133.811978</v>
+      </c>
+      <c r="R73" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 池田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -31175,9 +33887,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P74" s="5" t="n"/>
-      <c r="Q74" s="5" t="n"/>
-      <c r="R74" s="5" t="n"/>
+      <c r="P74" s="5" t="n">
+        <v>34.096349</v>
+      </c>
+      <c r="Q74" s="5" t="n">
+        <v>132.974562</v>
+      </c>
+      <c r="R74" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱波止浜変電所</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
@@ -31239,9 +33959,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P75" s="5" t="n"/>
-      <c r="Q75" s="5" t="n"/>
-      <c r="R75" s="5" t="n"/>
+      <c r="P75" s="5" t="n">
+        <v>34.078698</v>
+      </c>
+      <c r="Q75" s="5" t="n">
+        <v>132.993931</v>
+      </c>
+      <c r="R75" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱ 浅川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -31303,9 +34031,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P76" s="5" t="n"/>
-      <c r="Q76" s="5" t="n"/>
-      <c r="R76" s="5" t="n"/>
+      <c r="P76" s="5" t="n">
+        <v>33.572227</v>
+      </c>
+      <c r="Q76" s="5" t="n">
+        <v>133.671541</v>
+      </c>
+      <c r="R76" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電（株）立田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
@@ -31367,9 +34103,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P77" s="5" t="n"/>
-      <c r="Q77" s="5" t="n"/>
-      <c r="R77" s="5" t="n"/>
+      <c r="P77" s="5" t="n">
+        <v>33.516807</v>
+      </c>
+      <c r="Q77" s="5" t="n">
+        <v>132.54872</v>
+      </c>
+      <c r="R77" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱若宮変電所</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -31431,9 +34175,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P78" s="5" t="n"/>
-      <c r="Q78" s="5" t="n"/>
-      <c r="R78" s="5" t="n"/>
+      <c r="P78" s="5" t="n">
+        <v>34.072451</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>134.51652</v>
+      </c>
+      <c r="R78" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱蔵本変電所</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
@@ -31495,9 +34247,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P79" s="5" t="n"/>
-      <c r="Q79" s="5" t="n"/>
-      <c r="R79" s="5" t="n"/>
+      <c r="P79" s="5" t="n">
+        <v>34.075719</v>
+      </c>
+      <c r="Q79" s="5" t="n">
+        <v>134.547214</v>
+      </c>
+      <c r="R79" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 藍場変電所</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -31623,9 +34383,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P81" s="5" t="n"/>
-      <c r="Q81" s="5" t="n"/>
-      <c r="R81" s="5" t="n"/>
+      <c r="P81" s="5" t="n">
+        <v>34.040491</v>
+      </c>
+      <c r="Q81" s="5" t="n">
+        <v>134.562146</v>
+      </c>
+      <c r="R81" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力雑賀変電所</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
@@ -31751,9 +34519,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P83" s="5" t="n"/>
-      <c r="Q83" s="5" t="n"/>
-      <c r="R83" s="5" t="n"/>
+      <c r="P83" s="5" t="n">
+        <v>36.446085</v>
+      </c>
+      <c r="Q83" s="5" t="n">
+        <v>136.512309</v>
+      </c>
+      <c r="R83" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 久常変電所</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
@@ -31879,9 +34655,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P85" s="5" t="n"/>
-      <c r="Q85" s="5" t="n"/>
-      <c r="R85" s="5" t="n"/>
+      <c r="P85" s="5" t="n">
+        <v>36.560296</v>
+      </c>
+      <c r="Q85" s="5" t="n">
+        <v>136.588867</v>
+      </c>
+      <c r="R85" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 安原変電所</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
@@ -31943,9 +34727,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P86" s="5" t="n"/>
-      <c r="Q86" s="5" t="n"/>
-      <c r="R86" s="5" t="n"/>
+      <c r="P86" s="5" t="n">
+        <v>36.062734</v>
+      </c>
+      <c r="Q86" s="5" t="n">
+        <v>136.237662</v>
+      </c>
+      <c r="R86" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 東福井変電所</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
@@ -32007,9 +34799,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P87" s="5" t="n"/>
-      <c r="Q87" s="5" t="n"/>
-      <c r="R87" s="5" t="n"/>
+      <c r="P87" s="5" t="n">
+        <v>33.984238</v>
+      </c>
+      <c r="Q87" s="5" t="n">
+        <v>133.554804</v>
+      </c>
+      <c r="R87" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力 朝日町変電所</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
@@ -32071,9 +34871,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P88" s="5" t="n"/>
-      <c r="Q88" s="5" t="n"/>
-      <c r="R88" s="5" t="n"/>
+      <c r="P88" s="5" t="n">
+        <v>34.083034</v>
+      </c>
+      <c r="Q88" s="5" t="n">
+        <v>133.640982</v>
+      </c>
+      <c r="R88" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱豊浜変電所</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
@@ -32199,9 +35007,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P90" s="5" t="n"/>
-      <c r="Q90" s="5" t="n"/>
-      <c r="R90" s="5" t="n"/>
+      <c r="P90" s="5" t="n">
+        <v>36.518291</v>
+      </c>
+      <c r="Q90" s="5" t="n">
+        <v>136.599066</v>
+      </c>
+      <c r="R90" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 下林変電所</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
@@ -32263,9 +35079,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P91" s="5" t="n"/>
-      <c r="Q91" s="5" t="n"/>
-      <c r="R91" s="5" t="n"/>
+      <c r="P91" s="5" t="n">
+        <v>36.060751</v>
+      </c>
+      <c r="Q91" s="5" t="n">
+        <v>136.508632</v>
+      </c>
+      <c r="R91" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 勝山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
@@ -32391,9 +35215,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P93" s="5" t="n"/>
-      <c r="Q93" s="5" t="n"/>
-      <c r="R93" s="5" t="n"/>
+      <c r="P93" s="5" t="n">
+        <v>36.619724</v>
+      </c>
+      <c r="Q93" s="5" t="n">
+        <v>136.657224</v>
+      </c>
+      <c r="R93" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 大浦変電所</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
@@ -32455,9 +35287,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P94" s="5" t="n"/>
-      <c r="Q94" s="5" t="n"/>
-      <c r="R94" s="5" t="n"/>
+      <c r="P94" s="5" t="n">
+        <v>36.254038</v>
+      </c>
+      <c r="Q94" s="5" t="n">
+        <v>136.366909</v>
+      </c>
+      <c r="R94" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 山中変電所</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
@@ -32519,9 +35359,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P95" s="5" t="n"/>
-      <c r="Q95" s="5" t="n"/>
-      <c r="R95" s="5" t="n"/>
+      <c r="P95" s="5" t="n">
+        <v>36.294259</v>
+      </c>
+      <c r="Q95" s="5" t="n">
+        <v>136.363277</v>
+      </c>
+      <c r="R95" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 山代変電所</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
@@ -32647,9 +35495,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P97" s="5" t="n"/>
-      <c r="Q97" s="5" t="n"/>
-      <c r="R97" s="5" t="n"/>
+      <c r="P97" s="5" t="n">
+        <v>36.851031</v>
+      </c>
+      <c r="Q97" s="5" t="n">
+        <v>136.956076</v>
+      </c>
+      <c r="R97" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 沖布変電所</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
@@ -32711,9 +35567,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P98" s="5" t="n"/>
-      <c r="Q98" s="5" t="n"/>
-      <c r="R98" s="5" t="n"/>
+      <c r="P98" s="5" t="n">
+        <v>35.874916</v>
+      </c>
+      <c r="Q98" s="5" t="n">
+        <v>136.162947</v>
+      </c>
+      <c r="R98" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 王子保変電所</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
@@ -32903,9 +35767,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P101" s="5" t="n"/>
-      <c r="Q101" s="5" t="n"/>
-      <c r="R101" s="5" t="n"/>
+      <c r="P101" s="5" t="n">
+        <v>36.774655</v>
+      </c>
+      <c r="Q101" s="5" t="n">
+        <v>137.036059</v>
+      </c>
+      <c r="R101" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 米島変電所</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
@@ -32967,9 +35839,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P102" s="5" t="n"/>
-      <c r="Q102" s="5" t="n"/>
-      <c r="R102" s="5" t="n"/>
+      <c r="P102" s="5" t="n">
+        <v>36.404747</v>
+      </c>
+      <c r="Q102" s="5" t="n">
+        <v>136.506929</v>
+      </c>
+      <c r="R102" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 荒木田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
@@ -33031,9 +35911,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P103" s="5" t="n"/>
-      <c r="Q103" s="5" t="n"/>
-      <c r="R103" s="5" t="n"/>
+      <c r="P103" s="5" t="n">
+        <v>35.645717</v>
+      </c>
+      <c r="Q103" s="5" t="n">
+        <v>136.045158</v>
+      </c>
+      <c r="R103" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 西敦賀変電所</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -33287,9 +36175,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P107" s="5" t="n"/>
-      <c r="Q107" s="5" t="n"/>
-      <c r="R107" s="5" t="n"/>
+      <c r="P107" s="5" t="n">
+        <v>33.407956</v>
+      </c>
+      <c r="Q107" s="5" t="n">
+        <v>133.300544</v>
+      </c>
+      <c r="R107" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 押岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
@@ -33415,9 +36311,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P109" s="5" t="n"/>
-      <c r="Q109" s="5" t="n"/>
-      <c r="R109" s="5" t="n"/>
+      <c r="P109" s="5" t="n">
+        <v>36.719024</v>
+      </c>
+      <c r="Q109" s="5" t="n">
+        <v>137.089335</v>
+      </c>
+      <c r="R109" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 小杉変電所</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
@@ -33479,9 +36383,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P110" s="5" t="n"/>
-      <c r="Q110" s="5" t="n"/>
-      <c r="R110" s="5" t="n"/>
+      <c r="P110" s="5" t="n">
+        <v>36.58354</v>
+      </c>
+      <c r="Q110" s="5" t="n">
+        <v>136.659118</v>
+      </c>
+      <c r="R110" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 浅野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
@@ -33543,9 +36455,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P111" s="5" t="n"/>
-      <c r="Q111" s="5" t="n"/>
-      <c r="R111" s="5" t="n"/>
+      <c r="P111" s="5" t="n">
+        <v>36.741157</v>
+      </c>
+      <c r="Q111" s="5" t="n">
+        <v>137.024608</v>
+      </c>
+      <c r="R111" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 高岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
@@ -33607,9 +36527,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P112" s="5" t="n"/>
-      <c r="Q112" s="5" t="n"/>
-      <c r="R112" s="5" t="n"/>
+      <c r="P112" s="5" t="n">
+        <v>36.814558</v>
+      </c>
+      <c r="Q112" s="5" t="n">
+        <v>137.410154</v>
+      </c>
+      <c r="R112" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 魚津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
@@ -33671,9 +36599,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P113" s="5" t="n"/>
-      <c r="Q113" s="5" t="n"/>
-      <c r="R113" s="5" t="n"/>
+      <c r="P113" s="5" t="n">
+        <v>33.939107</v>
+      </c>
+      <c r="Q113" s="5" t="n">
+        <v>133.191379</v>
+      </c>
+      <c r="R113" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱ひうち変電所</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
@@ -33735,9 +36671,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P114" s="5" t="n"/>
-      <c r="Q114" s="5" t="n"/>
-      <c r="R114" s="5" t="n"/>
+      <c r="P114" s="5" t="n">
+        <v>34.288336</v>
+      </c>
+      <c r="Q114" s="5" t="n">
+        <v>134.03217</v>
+      </c>
+      <c r="R114" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 仏生山変電所</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
@@ -33799,9 +36743,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P115" s="5" t="n"/>
-      <c r="Q115" s="5" t="n"/>
-      <c r="R115" s="5" t="n"/>
+      <c r="P115" s="5" t="n">
+        <v>33.6034</v>
+      </c>
+      <c r="Q115" s="5" t="n">
+        <v>133.653586</v>
+      </c>
+      <c r="R115" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱南国変電所</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
@@ -33863,9 +36815,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P116" s="5" t="n"/>
-      <c r="Q116" s="5" t="n"/>
-      <c r="R116" s="5" t="n"/>
+      <c r="P116" s="5" t="n">
+        <v>34.039106</v>
+      </c>
+      <c r="Q116" s="5" t="n">
+        <v>133.011163</v>
+      </c>
+      <c r="R116" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 富田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
@@ -33927,9 +36887,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P117" s="5" t="n"/>
-      <c r="Q117" s="5" t="n"/>
-      <c r="R117" s="5" t="n"/>
+      <c r="P117" s="5" t="n">
+        <v>34.342452</v>
+      </c>
+      <c r="Q117" s="5" t="n">
+        <v>134.124655</v>
+      </c>
+      <c r="R117" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 屋島変電所</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
@@ -33991,9 +36959,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P118" s="5" t="n"/>
-      <c r="Q118" s="5" t="n"/>
-      <c r="R118" s="5" t="n"/>
+      <c r="P118" s="5" t="n">
+        <v>32.966261</v>
+      </c>
+      <c r="Q118" s="5" t="n">
+        <v>132.569052</v>
+      </c>
+      <c r="R118" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 御荘変電所</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
@@ -34055,9 +37031,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P119" s="5" t="n"/>
-      <c r="Q119" s="5" t="n"/>
-      <c r="R119" s="5" t="n"/>
+      <c r="P119" s="5" t="n">
+        <v>33.550437</v>
+      </c>
+      <c r="Q119" s="5" t="n">
+        <v>133.747751</v>
+      </c>
+      <c r="R119" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 香我美変電所</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
@@ -34119,9 +37103,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P120" s="5" t="n"/>
-      <c r="Q120" s="5" t="n"/>
-      <c r="R120" s="5" t="n"/>
+      <c r="P120" s="5" t="n">
+        <v>36.700251</v>
+      </c>
+      <c r="Q120" s="5" t="n">
+        <v>137.356283</v>
+      </c>
+      <c r="R120" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 上市変電所</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
@@ -34183,9 +37175,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P121" s="5" t="n"/>
-      <c r="Q121" s="5" t="n"/>
-      <c r="R121" s="5" t="n"/>
+      <c r="P121" s="5" t="n">
+        <v>36.569702</v>
+      </c>
+      <c r="Q121" s="5" t="n">
+        <v>136.96577</v>
+      </c>
+      <c r="R121" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 井波変電所</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
@@ -34247,9 +37247,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P122" s="5" t="n"/>
-      <c r="Q122" s="5" t="n"/>
-      <c r="R122" s="5" t="n"/>
+      <c r="P122" s="5" t="n">
+        <v>35.996314</v>
+      </c>
+      <c r="Q122" s="5" t="n">
+        <v>136.502458</v>
+      </c>
+      <c r="R122" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 友江変電所</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
@@ -34311,9 +37319,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P123" s="5" t="n"/>
-      <c r="Q123" s="5" t="n"/>
-      <c r="R123" s="5" t="n"/>
+      <c r="P123" s="5" t="n">
+        <v>36.686413</v>
+      </c>
+      <c r="Q123" s="5" t="n">
+        <v>136.981191</v>
+      </c>
+      <c r="R123" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 戸出変電所</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
@@ -34375,9 +37391,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P124" s="5" t="n"/>
-      <c r="Q124" s="5" t="n"/>
-      <c r="R124" s="5" t="n"/>
+      <c r="P124" s="5" t="n">
+        <v>36.781715</v>
+      </c>
+      <c r="Q124" s="5" t="n">
+        <v>137.08093</v>
+      </c>
+      <c r="R124" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 新湊変電所</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
@@ -34439,9 +37463,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P125" s="5" t="n"/>
-      <c r="Q125" s="5" t="n"/>
-      <c r="R125" s="5" t="n"/>
+      <c r="P125" s="5" t="n">
+        <v>36.773855</v>
+      </c>
+      <c r="Q125" s="5" t="n">
+        <v>137.381739</v>
+      </c>
+      <c r="R125" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 東滑川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
@@ -34503,9 +37535,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P126" s="5" t="n"/>
-      <c r="Q126" s="5" t="n"/>
-      <c r="R126" s="5" t="n"/>
+      <c r="P126" s="5" t="n">
+        <v>36.733874</v>
+      </c>
+      <c r="Q126" s="5" t="n">
+        <v>137.293756</v>
+      </c>
+      <c r="R126" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 水橋変電所</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
@@ -34567,9 +37607,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P127" s="5" t="n"/>
-      <c r="Q127" s="5" t="n"/>
-      <c r="R127" s="5" t="n"/>
+      <c r="P127" s="5" t="n">
+        <v>36.597641</v>
+      </c>
+      <c r="Q127" s="5" t="n">
+        <v>136.925697</v>
+      </c>
+      <c r="R127" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 福野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
@@ -34631,9 +37679,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P128" s="5" t="n"/>
-      <c r="Q128" s="5" t="n"/>
-      <c r="R128" s="5" t="n"/>
+      <c r="P128" s="5" t="n">
+        <v>37.389606</v>
+      </c>
+      <c r="Q128" s="5" t="n">
+        <v>136.902988</v>
+      </c>
+      <c r="R128" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電 輪島変電所</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
@@ -34759,9 +37815,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P130" s="5" t="n"/>
-      <c r="Q130" s="5" t="n"/>
-      <c r="R130" s="5" t="n"/>
+      <c r="P130" s="5" t="n">
+        <v>33.578716</v>
+      </c>
+      <c r="Q130" s="5" t="n">
+        <v>133.568652</v>
+      </c>
+      <c r="R130" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 一宮変電所</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
@@ -34887,9 +37951,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P132" s="5" t="n"/>
-      <c r="Q132" s="5" t="n"/>
-      <c r="R132" s="5" t="n"/>
+      <c r="P132" s="5" t="n">
+        <v>33.384324</v>
+      </c>
+      <c r="Q132" s="5" t="n">
+        <v>132.426886</v>
+      </c>
+      <c r="R132" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 三瓶変電所</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
@@ -35079,9 +38151,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P135" s="5" t="n"/>
-      <c r="Q135" s="5" t="n"/>
-      <c r="R135" s="5" t="n"/>
+      <c r="P135" s="5" t="n">
+        <v>33.279898</v>
+      </c>
+      <c r="Q135" s="5" t="n">
+        <v>132.541738</v>
+      </c>
+      <c r="R135" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 吉田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
@@ -35143,9 +38223,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P136" s="5" t="n"/>
-      <c r="Q136" s="5" t="n"/>
-      <c r="R136" s="5" t="n"/>
+      <c r="P136" s="5" t="n">
+        <v>33.968242</v>
+      </c>
+      <c r="Q136" s="5" t="n">
+        <v>134.351555</v>
+      </c>
+      <c r="R136" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 寄井変電所</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
@@ -35207,9 +38295,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P137" s="5" t="n"/>
-      <c r="Q137" s="5" t="n"/>
-      <c r="R137" s="5" t="n"/>
+      <c r="P137" s="5" t="n">
+        <v>33.53145</v>
+      </c>
+      <c r="Q137" s="5" t="n">
+        <v>132.589904</v>
+      </c>
+      <c r="R137" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱徳森変電所</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
@@ -35271,9 +38367,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P138" s="5" t="n"/>
-      <c r="Q138" s="5" t="n"/>
-      <c r="R138" s="5" t="n"/>
+      <c r="P138" s="5" t="n">
+        <v>33.737081</v>
+      </c>
+      <c r="Q138" s="5" t="n">
+        <v>134.526897</v>
+      </c>
+      <c r="R138" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 日和佐変電所</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
@@ -35527,9 +38631,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P142" s="5" t="n"/>
-      <c r="Q142" s="5" t="n"/>
-      <c r="R142" s="5" t="n"/>
+      <c r="P142" s="5" t="n">
+        <v>33.365949</v>
+      </c>
+      <c r="Q142" s="5" t="n">
+        <v>132.634424</v>
+      </c>
+      <c r="R142" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 野村変電所</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
@@ -35591,9 +38703,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P143" s="5" t="n"/>
-      <c r="Q143" s="5" t="n"/>
-      <c r="R143" s="5" t="n"/>
+      <c r="P143" s="5" t="n">
+        <v>33.618487</v>
+      </c>
+      <c r="Q143" s="5" t="n">
+        <v>132.49442</v>
+      </c>
+      <c r="R143" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 長浜変電所</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
@@ -35719,9 +38839,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P145" s="5" t="n"/>
-      <c r="Q145" s="5" t="n"/>
-      <c r="R145" s="5" t="n"/>
+      <c r="P145" s="5" t="n">
+        <v>36.998849</v>
+      </c>
+      <c r="Q145" s="5" t="n">
+        <v>136.937691</v>
+      </c>
+      <c r="R145" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 徳田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
@@ -35783,9 +38911,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P146" s="5" t="n"/>
-      <c r="Q146" s="5" t="n"/>
-      <c r="R146" s="5" t="n"/>
+      <c r="P146" s="5" t="n">
+        <v>36.012916</v>
+      </c>
+      <c r="Q146" s="5" t="n">
+        <v>136.26277</v>
+      </c>
+      <c r="R146" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 東郷変電所</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
@@ -35847,9 +38983,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P147" s="5" t="n"/>
-      <c r="Q147" s="5" t="n"/>
-      <c r="R147" s="5" t="n"/>
+      <c r="P147" s="5" t="n">
+        <v>36.452508</v>
+      </c>
+      <c r="Q147" s="5" t="n">
+        <v>136.463552</v>
+      </c>
+      <c r="R147" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 根上変電所</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
@@ -35911,9 +39055,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P148" s="5" t="n"/>
-      <c r="Q148" s="5" t="n"/>
-      <c r="R148" s="5" t="n"/>
+      <c r="P148" s="5" t="n">
+        <v>35.965934</v>
+      </c>
+      <c r="Q148" s="5" t="n">
+        <v>136.187874</v>
+      </c>
+      <c r="R148" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 水落変電所</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
@@ -35975,9 +39127,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P149" s="5" t="n"/>
-      <c r="Q149" s="5" t="n"/>
-      <c r="R149" s="5" t="n"/>
+      <c r="P149" s="5" t="n">
+        <v>36.345039</v>
+      </c>
+      <c r="Q149" s="5" t="n">
+        <v>136.514587</v>
+      </c>
+      <c r="R149" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 沢変電所</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
@@ -36039,9 +39199,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P150" s="5" t="n"/>
-      <c r="Q150" s="5" t="n"/>
-      <c r="R150" s="5" t="n"/>
+      <c r="P150" s="5" t="n">
+        <v>35.790526</v>
+      </c>
+      <c r="Q150" s="5" t="n">
+        <v>136.202552</v>
+      </c>
+      <c r="R150" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 湯尾変電所</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
@@ -36103,9 +39271,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P151" s="5" t="n"/>
-      <c r="Q151" s="5" t="n"/>
-      <c r="R151" s="5" t="n"/>
+      <c r="P151" s="5" t="n">
+        <v>36.330452</v>
+      </c>
+      <c r="Q151" s="5" t="n">
+        <v>136.366901</v>
+      </c>
+      <c r="R151" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 片山津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
@@ -36167,9 +39343,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P152" s="5" t="n"/>
-      <c r="Q152" s="5" t="n"/>
-      <c r="R152" s="5" t="n"/>
+      <c r="P152" s="5" t="n">
+        <v>35.901872</v>
+      </c>
+      <c r="Q152" s="5" t="n">
+        <v>136.155796</v>
+      </c>
+      <c r="R152" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 西武生変電所</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
@@ -36231,9 +39415,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P153" s="5" t="n"/>
-      <c r="Q153" s="5" t="n"/>
-      <c r="R153" s="5" t="n"/>
+      <c r="P153" s="5" t="n">
+        <v>36.533852</v>
+      </c>
+      <c r="Q153" s="5" t="n">
+        <v>136.655177</v>
+      </c>
+      <c r="R153" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 長坂変電所</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
@@ -36295,9 +39487,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P154" s="5" t="n"/>
-      <c r="Q154" s="5" t="n"/>
-      <c r="R154" s="5" t="n"/>
+      <c r="P154" s="5" t="n">
+        <v>33.329098</v>
+      </c>
+      <c r="Q154" s="5" t="n">
+        <v>133.216545</v>
+      </c>
+      <c r="R154" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 久礼変電所</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
@@ -36423,9 +39623,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P156" s="5" t="n"/>
-      <c r="Q156" s="5" t="n"/>
-      <c r="R156" s="5" t="n"/>
+      <c r="P156" s="5" t="n">
+        <v>33.504379</v>
+      </c>
+      <c r="Q156" s="5" t="n">
+        <v>133.541516</v>
+      </c>
+      <c r="R156" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 桂浜変電所</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
@@ -36487,9 +39695,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P157" s="5" t="n"/>
-      <c r="Q157" s="5" t="n"/>
-      <c r="R157" s="5" t="n"/>
+      <c r="P157" s="5" t="n">
+        <v>34.219577</v>
+      </c>
+      <c r="Q157" s="5" t="n">
+        <v>133.669116</v>
+      </c>
+      <c r="R157" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電（株）詫間変電所</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
@@ -36551,9 +39767,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P158" s="5" t="n"/>
-      <c r="Q158" s="5" t="n"/>
-      <c r="R158" s="5" t="n"/>
+      <c r="P158" s="5" t="n">
+        <v>36.148739</v>
+      </c>
+      <c r="Q158" s="5" t="n">
+        <v>136.26783</v>
+      </c>
+      <c r="R158" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 丸岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
@@ -36615,9 +39839,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P159" s="5" t="n"/>
-      <c r="Q159" s="5" t="n"/>
-      <c r="R159" s="5" t="n"/>
+      <c r="P159" s="5" t="n">
+        <v>37.342891</v>
+      </c>
+      <c r="Q159" s="5" t="n">
+        <v>137.232154</v>
+      </c>
+      <c r="R159" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 内浦変電所</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
@@ -36679,9 +39911,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P160" s="5" t="n"/>
-      <c r="Q160" s="5" t="n"/>
-      <c r="R160" s="5" t="n"/>
+      <c r="P160" s="5" t="n">
+        <v>37.073446</v>
+      </c>
+      <c r="Q160" s="5" t="n">
+        <v>136.929888</v>
+      </c>
+      <c r="R160" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 和倉変電所</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
@@ -36871,9 +40111,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P163" s="5" t="n"/>
-      <c r="Q163" s="5" t="n"/>
-      <c r="R163" s="5" t="n"/>
+      <c r="P163" s="5" t="n">
+        <v>35.976563</v>
+      </c>
+      <c r="Q163" s="5" t="n">
+        <v>136.505954</v>
+      </c>
+      <c r="R163" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 大野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
@@ -36935,9 +40183,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P164" s="5" t="n"/>
-      <c r="Q164" s="5" t="n"/>
-      <c r="R164" s="5" t="n"/>
+      <c r="P164" s="5" t="n">
+        <v>36.705142</v>
+      </c>
+      <c r="Q164" s="5" t="n">
+        <v>137.020521</v>
+      </c>
+      <c r="R164" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 大門変電所</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
@@ -36999,9 +40255,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P165" s="5" t="n"/>
-      <c r="Q165" s="5" t="n"/>
-      <c r="R165" s="5" t="n"/>
+      <c r="P165" s="5" t="n">
+        <v>36.719629</v>
+      </c>
+      <c r="Q165" s="5" t="n">
+        <v>136.704795</v>
+      </c>
+      <c r="R165" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 宇ノ気変電所</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
@@ -37063,9 +40327,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P166" s="5" t="n"/>
-      <c r="Q166" s="5" t="n"/>
-      <c r="R166" s="5" t="n"/>
+      <c r="P166" s="5" t="n">
+        <v>36.822669</v>
+      </c>
+      <c r="Q166" s="5" t="n">
+        <v>137.57071</v>
+      </c>
+      <c r="R166" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 宇奈月変電所</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
@@ -37127,9 +40399,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P167" s="5" t="n"/>
-      <c r="Q167" s="5" t="n"/>
-      <c r="R167" s="5" t="n"/>
+      <c r="P167" s="5" t="n">
+        <v>37.141844</v>
+      </c>
+      <c r="Q167" s="5" t="n">
+        <v>136.735219</v>
+      </c>
+      <c r="R167" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 富来変電所</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
@@ -37191,9 +40471,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P168" s="5" t="n"/>
-      <c r="Q168" s="5" t="n"/>
-      <c r="R168" s="5" t="n"/>
+      <c r="P168" s="5" t="n">
+        <v>36.646724</v>
+      </c>
+      <c r="Q168" s="5" t="n">
+        <v>137.002611</v>
+      </c>
+      <c r="R168" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 庄西変電所</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
@@ -37255,9 +40543,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P169" s="5" t="n"/>
-      <c r="Q169" s="5" t="n"/>
-      <c r="R169" s="5" t="n"/>
+      <c r="P169" s="5" t="n">
+        <v>36.752388</v>
+      </c>
+      <c r="Q169" s="5" t="n">
+        <v>136.986438</v>
+      </c>
+      <c r="R169" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 早川変電所</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
@@ -37319,9 +40615,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P170" s="5" t="n"/>
-      <c r="Q170" s="5" t="n"/>
-      <c r="R170" s="5" t="n"/>
+      <c r="P170" s="5" t="n">
+        <v>36.120673</v>
+      </c>
+      <c r="Q170" s="5" t="n">
+        <v>136.228741</v>
+      </c>
+      <c r="R170" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 春江変電所</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
@@ -37383,9 +40687,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P171" s="5" t="n"/>
-      <c r="Q171" s="5" t="n"/>
-      <c r="R171" s="5" t="n"/>
+      <c r="P171" s="5" t="n">
+        <v>36.844998</v>
+      </c>
+      <c r="Q171" s="5" t="n">
+        <v>136.992819</v>
+      </c>
+      <c r="R171" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 氷見変電所</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
@@ -37447,9 +40759,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P172" s="5" t="n"/>
-      <c r="Q172" s="5" t="n"/>
-      <c r="R172" s="5" t="n"/>
+      <c r="P172" s="5" t="n">
+        <v>36.945281</v>
+      </c>
+      <c r="Q172" s="5" t="n">
+        <v>137.561627</v>
+      </c>
+      <c r="R172" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 泊変電所</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
@@ -37511,9 +40831,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P173" s="5" t="n"/>
-      <c r="Q173" s="5" t="n"/>
-      <c r="R173" s="5" t="n"/>
+      <c r="P173" s="5" t="n">
+        <v>36.64988</v>
+      </c>
+      <c r="Q173" s="5" t="n">
+        <v>136.718101</v>
+      </c>
+      <c r="R173" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 津幡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
@@ -37575,9 +40903,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P174" s="5" t="n"/>
-      <c r="Q174" s="5" t="n"/>
-      <c r="R174" s="5" t="n"/>
+      <c r="P174" s="5" t="n">
+        <v>36.63143</v>
+      </c>
+      <c r="Q174" s="5" t="n">
+        <v>136.883015</v>
+      </c>
+      <c r="R174" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 浅地変電所</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
@@ -37639,9 +40975,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P175" s="5" t="n"/>
-      <c r="Q175" s="5" t="n"/>
-      <c r="R175" s="5" t="n"/>
+      <c r="P175" s="5" t="n">
+        <v>36.63666</v>
+      </c>
+      <c r="Q175" s="5" t="n">
+        <v>136.955854</v>
+      </c>
+      <c r="R175" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 砺波変電所</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
@@ -37703,9 +41047,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P176" s="5" t="n"/>
-      <c r="Q176" s="5" t="n"/>
-      <c r="R176" s="5" t="n"/>
+      <c r="P176" s="5" t="n">
+        <v>36.708082</v>
+      </c>
+      <c r="Q176" s="5" t="n">
+        <v>136.938529</v>
+      </c>
+      <c r="R176" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電 福岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
@@ -37767,9 +41119,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P177" s="5" t="n"/>
-      <c r="Q177" s="5" t="n"/>
-      <c r="R177" s="5" t="n"/>
+      <c r="P177" s="5" t="n">
+        <v>36.323837</v>
+      </c>
+      <c r="Q177" s="5" t="n">
+        <v>136.409682</v>
+      </c>
+      <c r="R177" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 箱宮変電所</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
@@ -37831,9 +41191,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P178" s="5" t="n"/>
-      <c r="Q178" s="5" t="n"/>
-      <c r="R178" s="5" t="n"/>
+      <c r="P178" s="5" t="n">
+        <v>36.363662</v>
+      </c>
+      <c r="Q178" s="5" t="n">
+        <v>136.431949</v>
+      </c>
+      <c r="R178" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 粟津変電所</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
@@ -37895,9 +41263,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P179" s="5" t="n"/>
-      <c r="Q179" s="5" t="n"/>
-      <c r="R179" s="5" t="n"/>
+      <c r="P179" s="5" t="n">
+        <v>36.896227</v>
+      </c>
+      <c r="Q179" s="5" t="n">
+        <v>136.78634</v>
+      </c>
+      <c r="R179" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 羽咋変電所</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
@@ -37959,9 +41335,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P180" s="5" t="n"/>
-      <c r="Q180" s="5" t="n"/>
-      <c r="R180" s="5" t="n"/>
+      <c r="P180" s="5" t="n">
+        <v>35.972313</v>
+      </c>
+      <c r="Q180" s="5" t="n">
+        <v>136.139609</v>
+      </c>
+      <c r="R180" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 西田中変電所</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
@@ -38023,9 +41407,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P181" s="5" t="n"/>
-      <c r="Q181" s="5" t="n"/>
-      <c r="R181" s="5" t="n"/>
+      <c r="P181" s="5" t="n">
+        <v>36.155245</v>
+      </c>
+      <c r="Q181" s="5" t="n">
+        <v>136.209874</v>
+      </c>
+      <c r="R181" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 西長田変電所</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
@@ -38087,9 +41479,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P182" s="5" t="n"/>
-      <c r="Q182" s="5" t="n"/>
-      <c r="R182" s="5" t="n"/>
+      <c r="P182" s="5" t="n">
+        <v>37.293032</v>
+      </c>
+      <c r="Q182" s="5" t="n">
+        <v>136.789526</v>
+      </c>
+      <c r="R182" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 門前変電所</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n">
@@ -38151,9 +41551,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P183" s="5" t="n"/>
-      <c r="Q183" s="5" t="n"/>
-      <c r="R183" s="5" t="n"/>
+      <c r="P183" s="5" t="n">
+        <v>36.771502</v>
+      </c>
+      <c r="Q183" s="5" t="n">
+        <v>136.734602</v>
+      </c>
+      <c r="R183" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 北陸電力送配電(株) 高松変電所</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n">
@@ -38279,9 +41687,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P185" s="5" t="n"/>
-      <c r="Q185" s="5" t="n"/>
-      <c r="R185" s="5" t="n"/>
+      <c r="P185" s="5" t="n">
+        <v>34.057627</v>
+      </c>
+      <c r="Q185" s="5" t="n">
+        <v>132.888519</v>
+      </c>
+      <c r="R185" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱亀岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n">
@@ -38343,9 +41759,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P186" s="5" t="n"/>
-      <c r="Q186" s="5" t="n"/>
-      <c r="R186" s="5" t="n"/>
+      <c r="P186" s="5" t="n">
+        <v>34.04951</v>
+      </c>
+      <c r="Q186" s="5" t="n">
+        <v>132.986829</v>
+      </c>
+      <c r="R186" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱ 今治変電所</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n">
@@ -38471,9 +41895,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P188" s="5" t="n"/>
-      <c r="Q188" s="5" t="n"/>
-      <c r="R188" s="5" t="n"/>
+      <c r="P188" s="5" t="n">
+        <v>34.22289</v>
+      </c>
+      <c r="Q188" s="5" t="n">
+        <v>133.835021</v>
+      </c>
+      <c r="R188" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電株式会社 垂水変電所</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n">
@@ -38535,9 +41967,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P189" s="5" t="n"/>
-      <c r="Q189" s="5" t="n"/>
-      <c r="R189" s="5" t="n"/>
+      <c r="P189" s="5" t="n">
+        <v>33.976635</v>
+      </c>
+      <c r="Q189" s="5" t="n">
+        <v>133.335458</v>
+      </c>
+      <c r="R189" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱多喜浜変電所</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n">
@@ -38663,9 +42103,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P191" s="5" t="n"/>
-      <c r="Q191" s="5" t="n"/>
-      <c r="R191" s="5" t="n"/>
+      <c r="P191" s="5" t="n">
+        <v>34.119711</v>
+      </c>
+      <c r="Q191" s="5" t="n">
+        <v>133.725904</v>
+      </c>
+      <c r="R191" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電（株）山本変電所</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n">
@@ -38727,9 +42175,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P192" s="5" t="n"/>
-      <c r="Q192" s="5" t="n"/>
-      <c r="R192" s="5" t="n"/>
+      <c r="P192" s="5" t="n">
+        <v>33.128875</v>
+      </c>
+      <c r="Q192" s="5" t="n">
+        <v>132.527341</v>
+      </c>
+      <c r="R192" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 岩松変電所</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n">
@@ -38791,9 +42247,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P193" s="5" t="n"/>
-      <c r="Q193" s="5" t="n"/>
-      <c r="R193" s="5" t="n"/>
+      <c r="P193" s="5" t="n">
+        <v>33.945025</v>
+      </c>
+      <c r="Q193" s="5" t="n">
+        <v>134.643376</v>
+      </c>
+      <c r="R193" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱平島変電所</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n">
@@ -39047,9 +42511,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P197" s="5" t="n"/>
-      <c r="Q197" s="5" t="n"/>
-      <c r="R197" s="5" t="n"/>
+      <c r="P197" s="5" t="n">
+        <v>32.782271</v>
+      </c>
+      <c r="Q197" s="5" t="n">
+        <v>132.949648</v>
+      </c>
+      <c r="R197" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱清水変電所</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n">
@@ -39111,9 +42583,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P198" s="5" t="n"/>
-      <c r="Q198" s="5" t="n"/>
-      <c r="R198" s="5" t="n"/>
+      <c r="P198" s="5" t="n">
+        <v>34.195041</v>
+      </c>
+      <c r="Q198" s="5" t="n">
+        <v>133.840501</v>
+      </c>
+      <c r="R198" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電株式会社 琴平変電所</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n">
@@ -39175,9 +42655,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P199" s="5" t="n"/>
-      <c r="Q199" s="5" t="n"/>
-      <c r="R199" s="5" t="n"/>
+      <c r="P199" s="5" t="n">
+        <v>33.428951</v>
+      </c>
+      <c r="Q199" s="5" t="n">
+        <v>134.009668</v>
+      </c>
+      <c r="R199" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 田野変電所</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n">
@@ -39239,9 +42727,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P200" s="5" t="n"/>
-      <c r="Q200" s="5" t="n"/>
-      <c r="R200" s="5" t="n"/>
+      <c r="P200" s="5" t="n">
+        <v>34.146817</v>
+      </c>
+      <c r="Q200" s="5" t="n">
+        <v>133.698409</v>
+      </c>
+      <c r="R200" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱豊中変電所</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n">
@@ -39303,9 +42799,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P201" s="5" t="n"/>
-      <c r="Q201" s="5" t="n"/>
-      <c r="R201" s="5" t="n"/>
+      <c r="P201" s="5" t="n">
+        <v>33.980287</v>
+      </c>
+      <c r="Q201" s="5" t="n">
+        <v>134.607412</v>
+      </c>
+      <c r="R201" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 赤石変電所</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n">
@@ -39367,9 +42871,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P202" s="5" t="n"/>
-      <c r="Q202" s="5" t="n"/>
-      <c r="R202" s="5" t="n"/>
+      <c r="P202" s="5" t="n">
+        <v>33.93474</v>
+      </c>
+      <c r="Q202" s="5" t="n">
+        <v>134.691624</v>
+      </c>
+      <c r="R202" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 辰巳変電所</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n">
@@ -39431,9 +42943,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P203" s="5" t="n"/>
-      <c r="Q203" s="5" t="n"/>
-      <c r="R203" s="5" t="n"/>
+      <c r="P203" s="5" t="n">
+        <v>33.497508</v>
+      </c>
+      <c r="Q203" s="5" t="n">
+        <v>133.432107</v>
+      </c>
+      <c r="R203" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電(株) 高岡変電所</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n">
@@ -39495,9 +43015,17 @@
           <t>地図で探す</t>
         </is>
       </c>
-      <c r="P204" s="5" t="n"/>
-      <c r="Q204" s="5" t="n"/>
-      <c r="R204" s="5" t="n"/>
+      <c r="P204" s="5" t="n">
+        <v>34.207688</v>
+      </c>
+      <c r="Q204" s="5" t="n">
+        <v>133.691512</v>
+      </c>
+      <c r="R204" s="5" t="inlineStr">
+        <is>
+          <t>Google Places(名称一致) 四国電力送配電㈱高瀬変電所</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n">
